--- a/july 2026/Daily Reports/Sales Reporting PPL - Rana Bilal Lahore (Final).xlsx
+++ b/july 2026/Daily Reports/Sales Reporting PPL - Rana Bilal Lahore (Final).xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA562335-AB18-4C36-9E92-B27079B839B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{469E47B7-9CBA-4E8D-9B12-0786A49780D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="76">
   <si>
     <t>Booking</t>
   </si>
@@ -253,7 +253,7 @@
     <t>Has Been resigned</t>
   </si>
   <si>
-    <t>Saleman Issu</t>
+    <t>On Leave</t>
   </si>
 </sst>
 </file>
@@ -1545,7 +1545,7 @@
     </row>
     <row r="2" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="94">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>2</v>
@@ -1666,59 +1666,57 @@
         <v>50</v>
       </c>
       <c r="H4" s="8">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I4" s="32">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.02</v>
+        <v>0.22</v>
       </c>
       <c r="J4" s="30">
         <v>40</v>
       </c>
       <c r="K4" s="31">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="L4" s="32">
         <f t="shared" ref="L4:L12" si="1">K4/J4</f>
-        <v>7.4999999999999997E-2</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="M4" s="30">
         <f t="shared" ref="M4:N12" si="2">K4/H4</f>
-        <v>3</v>
+        <v>1.1818181818181819</v>
       </c>
       <c r="N4" s="33">
         <f t="shared" si="2"/>
-        <v>3.75</v>
+        <v>1.4772727272727273</v>
       </c>
       <c r="O4" s="30">
         <v>12</v>
       </c>
-      <c r="P4" s="96">
-        <v>8</v>
-      </c>
+      <c r="P4" s="96"/>
       <c r="Q4" s="32">
         <f t="shared" ref="Q4:Q12" si="3">P4/O4</f>
-        <v>0.66666666666666663</v>
+        <v>0</v>
       </c>
       <c r="R4" s="30">
         <v>8</v>
       </c>
-      <c r="S4" s="96">
-        <v>13.75</v>
-      </c>
+      <c r="S4" s="96"/>
       <c r="T4" s="32">
         <f t="shared" ref="T4:T12" si="4">S4/R4</f>
-        <v>1.71875</v>
-      </c>
-      <c r="U4" s="30">
+        <v>0</v>
+      </c>
+      <c r="U4" s="30" t="e">
         <f t="shared" ref="U4:V12" si="5">S4/P4</f>
-        <v>1.71875</v>
-      </c>
-      <c r="V4" s="33">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V4" s="33" t="e">
         <f t="shared" si="5"/>
-        <v>2.578125</v>
-      </c>
-      <c r="W4" s="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W4" s="34" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="5" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="35" t="s">
@@ -1743,57 +1741,57 @@
         <v>50</v>
       </c>
       <c r="H5" s="12">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="I5" s="13">
         <f t="shared" si="0"/>
-        <v>0.18</v>
+        <v>0.36</v>
       </c>
       <c r="J5" s="30">
         <v>30</v>
       </c>
       <c r="K5" s="12">
-        <v>8.6999999999999993</v>
+        <v>21</v>
       </c>
       <c r="L5" s="13">
         <f t="shared" si="1"/>
-        <v>0.28999999999999998</v>
+        <v>0.7</v>
       </c>
       <c r="M5" s="11">
         <f t="shared" si="2"/>
-        <v>0.96666666666666656</v>
+        <v>1.1666666666666667</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="2"/>
-        <v>1.6111111111111112</v>
+        <v>1.9444444444444444</v>
       </c>
       <c r="O5" s="30">
         <v>7</v>
       </c>
       <c r="P5" s="97">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q5" s="13">
         <f t="shared" si="3"/>
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
       <c r="R5" s="30">
         <v>13</v>
       </c>
       <c r="S5" s="97">
-        <v>6.37</v>
+        <v>7</v>
       </c>
       <c r="T5" s="13">
         <f t="shared" si="4"/>
-        <v>0.49</v>
+        <v>0.53846153846153844</v>
       </c>
       <c r="U5" s="11">
         <f t="shared" si="5"/>
-        <v>1.274</v>
+        <v>1</v>
       </c>
       <c r="V5" s="14">
         <f t="shared" si="5"/>
-        <v>0.68599999999999994</v>
+        <v>0.53846153846153844</v>
       </c>
       <c r="W5" s="34"/>
     </row>
@@ -1914,9 +1912,7 @@
       <c r="O7" s="30">
         <v>5</v>
       </c>
-      <c r="P7" s="97">
-        <v>0</v>
-      </c>
+      <c r="P7" s="97"/>
       <c r="Q7" s="13">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -1924,9 +1920,7 @@
       <c r="R7" s="30">
         <v>5</v>
       </c>
-      <c r="S7" s="97">
-        <v>0</v>
-      </c>
+      <c r="S7" s="97"/>
       <c r="T7" s="13">
         <f t="shared" si="4"/>
         <v>0</v>
@@ -1966,57 +1960,57 @@
         <v>50</v>
       </c>
       <c r="H8" s="12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I8" s="13">
         <f t="shared" si="0"/>
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="J8" s="30">
         <v>20</v>
       </c>
       <c r="K8" s="12">
-        <v>11.7</v>
+        <v>15</v>
       </c>
       <c r="L8" s="13">
         <f t="shared" si="1"/>
-        <v>0.58499999999999996</v>
+        <v>0.75</v>
       </c>
       <c r="M8" s="11">
         <f t="shared" si="2"/>
-        <v>1.2999999999999998</v>
+        <v>1.875</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="2"/>
-        <v>3.25</v>
+        <v>4.6875</v>
       </c>
       <c r="O8" s="30">
         <v>15</v>
       </c>
       <c r="P8" s="97">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q8" s="13">
         <f t="shared" si="3"/>
-        <v>0.73333333333333328</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="R8" s="30">
         <v>15</v>
       </c>
       <c r="S8" s="97">
-        <v>20.03</v>
+        <v>11</v>
       </c>
       <c r="T8" s="13">
         <f t="shared" si="4"/>
-        <v>1.3353333333333335</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="U8" s="11">
         <f t="shared" si="5"/>
-        <v>1.820909090909091</v>
+        <v>1.375</v>
       </c>
       <c r="V8" s="14">
         <f t="shared" si="5"/>
-        <v>1.8209090909090913</v>
+        <v>1.375</v>
       </c>
       <c r="W8" s="34"/>
     </row>
@@ -2067,20 +2061,24 @@
         <f t="shared" ref="O9:O10" si="6">H9</f>
         <v>0</v>
       </c>
-      <c r="P9" s="97"/>
+      <c r="P9" s="97">
+        <v>6</v>
+      </c>
       <c r="Q9" s="13" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R9" s="30"/>
-      <c r="S9" s="97"/>
+      <c r="S9" s="97">
+        <v>74</v>
+      </c>
       <c r="T9" s="13" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U9" s="11" t="e">
+      <c r="U9" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>12.333333333333334</v>
       </c>
       <c r="V9" s="14" t="e">
         <f t="shared" si="5"/>
@@ -2121,7 +2119,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="12">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L10" s="13" t="e">
         <f t="shared" si="1"/>
@@ -2129,7 +2127,7 @@
       </c>
       <c r="M10" s="11">
         <f t="shared" si="2"/>
-        <v>12.666666666666666</v>
+        <v>12.333333333333334</v>
       </c>
       <c r="N10" s="14" t="e">
         <f t="shared" si="2"/>
@@ -2139,24 +2137,20 @@
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="P10" s="97">
-        <v>3</v>
-      </c>
+      <c r="P10" s="97"/>
       <c r="Q10" s="13">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R10" s="30"/>
-      <c r="S10" s="97">
-        <v>23</v>
-      </c>
+      <c r="S10" s="97"/>
       <c r="T10" s="13" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U10" s="11">
+      <c r="U10" s="11" t="e">
         <f t="shared" si="5"/>
-        <v>7.666666666666667</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="V10" s="14" t="e">
         <f t="shared" si="5"/>
@@ -2186,30 +2180,26 @@
       <c r="G11" s="30">
         <v>50</v>
       </c>
-      <c r="H11" s="12">
-        <v>17</v>
-      </c>
+      <c r="H11" s="12"/>
       <c r="I11" s="13">
         <f t="shared" si="0"/>
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="J11" s="30">
         <v>200</v>
       </c>
-      <c r="K11" s="12">
-        <v>28</v>
-      </c>
+      <c r="K11" s="12"/>
       <c r="L11" s="13">
         <f t="shared" si="1"/>
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="M11" s="11">
+        <v>0</v>
+      </c>
+      <c r="M11" s="11" t="e">
         <f t="shared" si="2"/>
-        <v>1.6470588235294117</v>
-      </c>
-      <c r="N11" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N11" s="14" t="e">
         <f t="shared" si="2"/>
-        <v>0.41176470588235298</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O11" s="30">
         <v>0</v>
@@ -2257,30 +2247,26 @@
       <c r="G12" s="30">
         <v>50</v>
       </c>
-      <c r="H12" s="12">
-        <v>3</v>
-      </c>
+      <c r="H12" s="12"/>
       <c r="I12" s="13">
         <f t="shared" si="0"/>
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="J12" s="30">
         <v>20</v>
       </c>
-      <c r="K12" s="12">
-        <v>4</v>
-      </c>
+      <c r="K12" s="12"/>
       <c r="L12" s="13">
         <f t="shared" si="1"/>
-        <v>0.2</v>
-      </c>
-      <c r="M12" s="11">
+        <v>0</v>
+      </c>
+      <c r="M12" s="11" t="e">
         <f t="shared" si="2"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="N12" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N12" s="14" t="e">
         <f t="shared" si="2"/>
-        <v>3.3333333333333335</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O12" s="30">
         <v>0</v>
@@ -2547,11 +2533,11 @@
       </c>
       <c r="H19" s="41">
         <f>SUM(H4:H18)</f>
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I19" s="42">
         <f t="shared" si="0"/>
-        <v>0.12</v>
+        <v>0.11466666666666667</v>
       </c>
       <c r="J19" s="40">
         <f>SUM(J4:J18)</f>
@@ -2559,15 +2545,15 @@
       </c>
       <c r="K19" s="41">
         <f>SUM(K4:K18)</f>
-        <v>131.4</v>
+        <v>123</v>
       </c>
       <c r="L19" s="42">
         <f t="shared" ref="L19" si="7">K19/J19</f>
-        <v>0.34129870129870132</v>
+        <v>0.31948051948051948</v>
       </c>
       <c r="M19" s="40">
         <f>K19/H19</f>
-        <v>2.92</v>
+        <v>2.86046511627907</v>
       </c>
       <c r="N19" s="43" t="e">
         <f>AVERAGE(N4:N18)</f>
@@ -2579,11 +2565,11 @@
       </c>
       <c r="P19" s="41">
         <f>SUM(P4:P18)</f>
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="Q19" s="42">
         <f t="shared" ref="Q19" si="8">P19/O19</f>
-        <v>0.50943396226415094</v>
+        <v>0.39622641509433965</v>
       </c>
       <c r="R19" s="40">
         <f>SUM(R4:R18)</f>
@@ -2591,15 +2577,15 @@
       </c>
       <c r="S19" s="41">
         <f>SUM(S4:S18)</f>
-        <v>63.150000000000006</v>
+        <v>92</v>
       </c>
       <c r="T19" s="42">
         <f t="shared" ref="T19" si="9">S19/R19</f>
-        <v>1.5402439024390244</v>
+        <v>2.2439024390243905</v>
       </c>
       <c r="U19" s="40">
         <f>S19/P19</f>
-        <v>2.338888888888889</v>
+        <v>4.3809523809523814</v>
       </c>
       <c r="V19" s="43" t="e">
         <f>AVERAGE(V4:V18)</f>
@@ -3461,11 +3447,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31" si="25">+H30+H25+H19</f>
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I31" s="22">
         <f t="shared" si="0"/>
-        <v>6.0495867768595044E-2</v>
+        <v>5.9834710743801652E-2</v>
       </c>
       <c r="J31" s="20">
         <f>+J30+J25+J19</f>
@@ -3473,15 +3459,15 @@
       </c>
       <c r="K31" s="21">
         <f t="shared" ref="K31" si="26">+K30+K25+K19</f>
-        <v>298.39999999999998</v>
+        <v>290</v>
       </c>
       <c r="L31" s="22">
         <f t="shared" si="10"/>
-        <v>0.11543520309477756</v>
+        <v>0.11218568665377177</v>
       </c>
       <c r="M31" s="20">
         <f>K31/H31</f>
-        <v>1.6306010928961747</v>
+        <v>1.6022099447513811</v>
       </c>
       <c r="N31" s="23" t="e">
         <f>AVERAGE(N30,N19,N25)</f>
@@ -3493,11 +3479,11 @@
       </c>
       <c r="P31" s="21">
         <f t="shared" ref="P31" si="27">+P30+P25+P19</f>
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="Q31" s="22">
         <f t="shared" si="12"/>
-        <v>0.69306930693069302</v>
+        <v>0.6633663366336634</v>
       </c>
       <c r="R31" s="20">
         <f>+R30+R25+R19</f>
@@ -3505,15 +3491,15 @@
       </c>
       <c r="S31" s="21">
         <f t="shared" ref="S31" si="28">+S30+S25+S19</f>
-        <v>193.15</v>
+        <v>222</v>
       </c>
       <c r="T31" s="22">
         <f t="shared" si="13"/>
-        <v>0.68982142857142859</v>
+        <v>0.79285714285714282</v>
       </c>
       <c r="U31" s="20">
         <f>S31/P31</f>
-        <v>1.3796428571428572</v>
+        <v>1.6567164179104477</v>
       </c>
       <c r="V31" s="23" t="e">
         <f>AVERAGE(V30,V19,V25)</f>
@@ -3578,18 +3564,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.33333333333333331</v>
+        <v>0.37037037037037035</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F2" s="94">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>40</v>
@@ -3684,35 +3670,35 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>5+9+9+11+10+9+11</f>
-        <v>64</v>
+        <f>5+9+9+11+10+9+11+8</f>
+        <v>72</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.10666666666666667</v>
+        <v>0.12</v>
       </c>
       <c r="J4" s="30">
         <v>575</v>
       </c>
       <c r="K4" s="8">
-        <f>8.5+9+12+11+17+6+12</f>
-        <v>75.5</v>
+        <f>8.5+9+12+11+17+6+12+14</f>
+        <v>89.5</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.13130434782608696</v>
+        <v>0.15565217391304348</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>499.5</v>
+        <v>485.5</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>27.75</v>
+        <v>28.558823529411764</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.1796875</v>
+        <v>1.2430555555555556</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3742,39 +3728,39 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>4+8+7+17+7+3+2</f>
-        <v>48</v>
+        <f>4+8+7+17+7+3+2+5</f>
+        <v>53</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>0.08</v>
+        <v>8.8333333333333333E-2</v>
       </c>
       <c r="J5" s="11">
         <v>550</v>
       </c>
       <c r="K5" s="12">
-        <f>6.6+9+5+6+11+4</f>
-        <v>41.6</v>
+        <f>6.6+9+5+6+11+4+6</f>
+        <v>47.6</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>7.563636363636364E-2</v>
+        <v>8.654545454545455E-2</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>508.4</v>
+        <v>502.4</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>28.244444444444444</v>
+        <v>29.552941176470586</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>0.8666666666666667</v>
+        <v>0.89811320754716983</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>0.94545454545454544</v>
+        <v>0.97975986277873073</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3825,7 +3811,7 @@
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29.647058823529413</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
@@ -3884,7 +3870,7 @@
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>28.772222222222222</v>
+        <v>30.464705882352941</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
@@ -3919,39 +3905,39 @@
         <v>600</v>
       </c>
       <c r="H8" s="12">
-        <f>10+10+0+14+6+10+11</f>
-        <v>61</v>
+        <f>10+10+0+14+6+10+11+11</f>
+        <v>72</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="0"/>
-        <v>0.10166666666666667</v>
+        <v>0.12</v>
       </c>
       <c r="J8" s="11">
         <v>575</v>
       </c>
       <c r="K8" s="12">
-        <f>14.1+13+0+46+23+10+12</f>
-        <v>118.1</v>
+        <f>14.1+13+0+46+23+10+12+20</f>
+        <v>138.1</v>
       </c>
       <c r="L8" s="71">
         <f t="shared" si="1"/>
-        <v>0.20539130434782607</v>
+        <v>0.24017391304347824</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>456.9</v>
+        <v>436.9</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>25.383333333333333</v>
+        <v>25.7</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
-        <v>1.9360655737704917</v>
+        <v>1.9180555555555554</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>2.0202423378474696</v>
+        <v>2.0014492753623188</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -3996,7 +3982,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>30.555555555555557</v>
+        <v>32.352941176470587</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4031,39 +4017,39 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <f>4+7+3+3</f>
-        <v>17</v>
+        <f>4+7+3+3+3</f>
+        <v>20</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>8.5000000000000006E-2</v>
+        <v>0.1</v>
       </c>
       <c r="J10" s="11">
         <v>4620</v>
       </c>
       <c r="K10" s="12">
-        <f>70+42+31+40</f>
-        <v>183</v>
+        <f>70+42+31+40+23</f>
+        <v>206</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>3.961038961038961E-2</v>
+        <v>4.4588744588744587E-2</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>4437</v>
+        <v>4414</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>246.5</v>
+        <v>259.64705882352939</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>10.764705882352942</v>
+        <v>10.3</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>0.46600458365164243</v>
+        <v>0.44588744588744583</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4114,7 +4100,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>35.111111111111114</v>
+        <v>37.176470588235297</v>
       </c>
       <c r="O11" s="72">
         <f t="shared" si="4"/>
@@ -4171,7 +4157,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>29.5</v>
+        <v>31.235294117647058</v>
       </c>
       <c r="O12" s="72">
         <f t="shared" si="4"/>
@@ -4371,7 +4357,7 @@
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>66.666666666666671</v>
+        <v>70.588235294117652</v>
       </c>
       <c r="O16" s="72">
         <f t="shared" si="10"/>
@@ -4478,11 +4464,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>288</v>
+        <v>315</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>5.7599999999999998E-2</v>
+        <v>6.3E-2</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4490,23 +4476,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>833.3</v>
+        <v>896.3</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>7.8097469540768502E-2</v>
+        <v>8.4001874414245545E-2</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>9836.7000000000007</v>
+        <v>9773.7000000000007</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>546.48333333333335</v>
+        <v>574.92352941176478</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>2.8934027777777778</v>
+        <v>2.8453968253968251</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4559,7 +4545,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>25.833333333333332</v>
+        <v>27.352941176470587</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4615,7 +4601,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>25.944444444444443</v>
+        <v>27.470588235294116</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4671,7 +4657,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>25.777777777777779</v>
+        <v>27.294117647058822</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4727,7 +4713,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>26.277777777777779</v>
+        <v>27.823529411764707</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4783,7 +4769,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>26.888888888888889</v>
+        <v>28.470588235294116</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4839,7 +4825,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>130.72222222222223</v>
+        <v>138.41176470588235</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4896,7 +4882,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>34.222222222222221</v>
+        <v>36.235294117647058</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -4952,7 +4938,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>31.444444444444443</v>
+        <v>33.294117647058826</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -5008,7 +4994,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>31.888888888888889</v>
+        <v>33.764705882352942</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5064,7 +5050,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5120,7 +5106,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>131.55555555555554</v>
+        <v>139.29411764705881</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5149,11 +5135,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>489</v>
+        <v>516</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>8.9724770642201829E-2</v>
+        <v>9.467889908256881E-2</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5161,23 +5147,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>1112.3</v>
+        <v>1175.3</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>7.0982769623484362E-2</v>
+        <v>7.5003190810465858E-2</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>14557.7</v>
+        <v>14494.7</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>808.76111111111118</v>
+        <v>852.62941176470588</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>2.2746421267893662</v>
+        <v>2.2777131782945736</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/july 2026/Daily Reports/Sales Reporting PPL - Rana Bilal Lahore (Final).xlsx
+++ b/july 2026/Daily Reports/Sales Reporting PPL - Rana Bilal Lahore (Final).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{469E47B7-9CBA-4E8D-9B12-0786A49780D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99C14041-1360-46A5-BEBA-529BCC44EFB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="76">
   <si>
     <t>Booking</t>
   </si>
@@ -250,10 +250,10 @@
     <t>Hamid</t>
   </si>
   <si>
-    <t>Has Been resigned</t>
-  </si>
-  <si>
     <t>On Leave</t>
+  </si>
+  <si>
+    <t>Resignd</t>
   </si>
 </sst>
 </file>
@@ -1545,7 +1545,7 @@
     </row>
     <row r="2" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="94">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>2</v>
@@ -1666,57 +1666,59 @@
         <v>50</v>
       </c>
       <c r="H4" s="8">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I4" s="32">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="J4" s="30">
         <v>40</v>
       </c>
       <c r="K4" s="31">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="L4" s="32">
         <f t="shared" ref="L4:L12" si="1">K4/J4</f>
-        <v>0.32500000000000001</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="M4" s="30">
         <f t="shared" ref="M4:N12" si="2">K4/H4</f>
-        <v>1.1818181818181819</v>
+        <v>2.625</v>
       </c>
       <c r="N4" s="33">
         <f t="shared" si="2"/>
-        <v>1.4772727272727273</v>
+        <v>3.28125</v>
       </c>
       <c r="O4" s="30">
         <v>12</v>
       </c>
-      <c r="P4" s="96"/>
+      <c r="P4" s="96">
+        <v>11</v>
+      </c>
       <c r="Q4" s="32">
         <f t="shared" ref="Q4:Q12" si="3">P4/O4</f>
-        <v>0</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="R4" s="30">
         <v>8</v>
       </c>
-      <c r="S4" s="96"/>
+      <c r="S4" s="96">
+        <v>7</v>
+      </c>
       <c r="T4" s="32">
         <f t="shared" ref="T4:T12" si="4">S4/R4</f>
-        <v>0</v>
-      </c>
-      <c r="U4" s="30" t="e">
+        <v>0.875</v>
+      </c>
+      <c r="U4" s="30">
         <f t="shared" ref="U4:V12" si="5">S4/P4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V4" s="33" t="e">
+        <v>0.63636363636363635</v>
+      </c>
+      <c r="V4" s="33">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W4" s="34" t="s">
-        <v>75</v>
-      </c>
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="W4" s="34"/>
     </row>
     <row r="5" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="35" t="s">
@@ -1740,58 +1742,54 @@
       <c r="G5" s="30">
         <v>50</v>
       </c>
-      <c r="H5" s="12">
-        <v>18</v>
-      </c>
+      <c r="H5" s="12"/>
       <c r="I5" s="13">
         <f t="shared" si="0"/>
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="J5" s="30">
         <v>30</v>
       </c>
-      <c r="K5" s="12">
-        <v>21</v>
-      </c>
+      <c r="K5" s="12"/>
       <c r="L5" s="13">
         <f t="shared" si="1"/>
-        <v>0.7</v>
-      </c>
-      <c r="M5" s="11">
+        <v>0</v>
+      </c>
+      <c r="M5" s="11" t="e">
         <f t="shared" si="2"/>
-        <v>1.1666666666666667</v>
-      </c>
-      <c r="N5" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N5" s="14" t="e">
         <f t="shared" si="2"/>
-        <v>1.9444444444444444</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O5" s="30">
         <v>7</v>
       </c>
       <c r="P5" s="97">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="Q5" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5" s="30">
         <v>13</v>
       </c>
       <c r="S5" s="97">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="T5" s="13">
         <f t="shared" si="4"/>
-        <v>0.53846153846153844</v>
+        <v>1.3076923076923077</v>
       </c>
       <c r="U5" s="11">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>1.2142857142857142</v>
       </c>
       <c r="V5" s="14">
         <f t="shared" si="5"/>
-        <v>0.53846153846153844</v>
+        <v>0.65384615384615385</v>
       </c>
       <c r="W5" s="34"/>
     </row>
@@ -1863,7 +1861,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="W6" s="34" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.5">
@@ -1934,7 +1932,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="W7" s="34" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.5">
@@ -1988,29 +1986,29 @@
         <v>15</v>
       </c>
       <c r="P8" s="97">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q8" s="13">
         <f t="shared" si="3"/>
-        <v>0.53333333333333333</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="R8" s="30">
         <v>15</v>
       </c>
       <c r="S8" s="97">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="T8" s="13">
         <f t="shared" si="4"/>
-        <v>0.73333333333333328</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="U8" s="11">
         <f t="shared" si="5"/>
-        <v>1.375</v>
+        <v>2</v>
       </c>
       <c r="V8" s="14">
         <f t="shared" si="5"/>
-        <v>1.375</v>
+        <v>2</v>
       </c>
       <c r="W8" s="34"/>
     </row>
@@ -2061,24 +2059,20 @@
         <f t="shared" ref="O9:O10" si="6">H9</f>
         <v>0</v>
       </c>
-      <c r="P9" s="97">
-        <v>6</v>
-      </c>
+      <c r="P9" s="97"/>
       <c r="Q9" s="13" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="R9" s="30"/>
-      <c r="S9" s="97">
-        <v>74</v>
-      </c>
+      <c r="S9" s="97"/>
       <c r="T9" s="13" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U9" s="11">
+      <c r="U9" s="11" t="e">
         <f t="shared" si="5"/>
-        <v>12.333333333333334</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="V9" s="14" t="e">
         <f t="shared" si="5"/>
@@ -2119,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="12">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="L10" s="13" t="e">
         <f t="shared" si="1"/>
@@ -2127,7 +2121,7 @@
       </c>
       <c r="M10" s="11">
         <f t="shared" si="2"/>
-        <v>12.333333333333334</v>
+        <v>8.5</v>
       </c>
       <c r="N10" s="14" t="e">
         <f t="shared" si="2"/>
@@ -2137,20 +2131,24 @@
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="P10" s="97"/>
+      <c r="P10" s="97">
+        <v>5</v>
+      </c>
       <c r="Q10" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="R10" s="30"/>
-      <c r="S10" s="97"/>
+      <c r="S10" s="97">
+        <v>74</v>
+      </c>
       <c r="T10" s="13" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U10" s="11" t="e">
+      <c r="U10" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>14.8</v>
       </c>
       <c r="V10" s="14" t="e">
         <f t="shared" si="5"/>
@@ -2533,11 +2531,11 @@
       </c>
       <c r="H19" s="41">
         <f>SUM(H4:H18)</f>
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="I19" s="42">
         <f t="shared" si="0"/>
-        <v>0.11466666666666667</v>
+        <v>5.8666666666666666E-2</v>
       </c>
       <c r="J19" s="40">
         <f>SUM(J4:J18)</f>
@@ -2545,15 +2543,15 @@
       </c>
       <c r="K19" s="41">
         <f>SUM(K4:K18)</f>
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="L19" s="42">
         <f t="shared" ref="L19" si="7">K19/J19</f>
-        <v>0.31948051948051948</v>
+        <v>0.22597402597402597</v>
       </c>
       <c r="M19" s="40">
         <f>K19/H19</f>
-        <v>2.86046511627907</v>
+        <v>3.9545454545454546</v>
       </c>
       <c r="N19" s="43" t="e">
         <f>AVERAGE(N4:N18)</f>
@@ -2565,11 +2563,11 @@
       </c>
       <c r="P19" s="41">
         <f>SUM(P4:P18)</f>
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="Q19" s="42">
         <f t="shared" ref="Q19" si="8">P19/O19</f>
-        <v>0.39622641509433965</v>
+        <v>0.69811320754716977</v>
       </c>
       <c r="R19" s="40">
         <f>SUM(R4:R18)</f>
@@ -2577,15 +2575,15 @@
       </c>
       <c r="S19" s="41">
         <f>SUM(S4:S18)</f>
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="T19" s="42">
         <f t="shared" ref="T19" si="9">S19/R19</f>
-        <v>2.2439024390243905</v>
+        <v>2.7317073170731709</v>
       </c>
       <c r="U19" s="40">
         <f>S19/P19</f>
-        <v>4.3809523809523814</v>
+        <v>3.0270270270270272</v>
       </c>
       <c r="V19" s="43" t="e">
         <f>AVERAGE(V4:V18)</f>
@@ -3447,11 +3445,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31" si="25">+H30+H25+H19</f>
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="I31" s="22">
         <f t="shared" si="0"/>
-        <v>5.9834710743801652E-2</v>
+        <v>5.2892561983471073E-2</v>
       </c>
       <c r="J31" s="20">
         <f>+J30+J25+J19</f>
@@ -3459,15 +3457,15 @@
       </c>
       <c r="K31" s="21">
         <f t="shared" ref="K31" si="26">+K30+K25+K19</f>
-        <v>290</v>
+        <v>254</v>
       </c>
       <c r="L31" s="22">
         <f t="shared" si="10"/>
-        <v>0.11218568665377177</v>
+        <v>9.8259187620889754E-2</v>
       </c>
       <c r="M31" s="20">
         <f>K31/H31</f>
-        <v>1.6022099447513811</v>
+        <v>1.5874999999999999</v>
       </c>
       <c r="N31" s="23" t="e">
         <f>AVERAGE(N30,N19,N25)</f>
@@ -3479,11 +3477,11 @@
       </c>
       <c r="P31" s="21">
         <f t="shared" ref="P31" si="27">+P30+P25+P19</f>
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="Q31" s="22">
         <f t="shared" si="12"/>
-        <v>0.6633663366336634</v>
+        <v>0.74257425742574257</v>
       </c>
       <c r="R31" s="20">
         <f>+R30+R25+R19</f>
@@ -3491,15 +3489,15 @@
       </c>
       <c r="S31" s="21">
         <f t="shared" ref="S31" si="28">+S30+S25+S19</f>
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="T31" s="22">
         <f t="shared" si="13"/>
-        <v>0.79285714285714282</v>
+        <v>0.86428571428571432</v>
       </c>
       <c r="U31" s="20">
         <f>S31/P31</f>
-        <v>1.6567164179104477</v>
+        <v>1.6133333333333333</v>
       </c>
       <c r="V31" s="23" t="e">
         <f>AVERAGE(V30,V19,V25)</f>
@@ -3564,18 +3562,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.37037037037037035</v>
+        <v>0.40740740740740738</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F2" s="94">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>40</v>
@@ -3694,7 +3692,7 @@
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>28.558823529411764</v>
+        <v>30.34375</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
@@ -3728,39 +3726,39 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>4+8+7+17+7+3+2+5</f>
-        <v>53</v>
+        <f>4+8+7+17+7+3+2+5+7</f>
+        <v>60</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>8.8333333333333333E-2</v>
+        <v>0.1</v>
       </c>
       <c r="J5" s="11">
         <v>550</v>
       </c>
       <c r="K5" s="12">
-        <f>6.6+9+5+6+11+4+6</f>
-        <v>47.6</v>
+        <f>6.6+9+5+6+11+4+6+7</f>
+        <v>54.6</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>8.654545454545455E-2</v>
+        <v>9.9272727272727276E-2</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>502.4</v>
+        <v>495.4</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>29.552941176470586</v>
+        <v>30.962499999999999</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>0.89811320754716983</v>
+        <v>0.91</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>0.97975986277873073</v>
+        <v>0.99272727272727268</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3811,7 +3809,7 @@
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>29.647058823529413</v>
+        <v>31.5</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
@@ -3870,7 +3868,7 @@
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>30.464705882352941</v>
+        <v>32.368749999999999</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
@@ -3905,39 +3903,39 @@
         <v>600</v>
       </c>
       <c r="H8" s="12">
-        <f>10+10+0+14+6+10+11+11</f>
-        <v>72</v>
+        <f>10+10+0+14+6+10+11+11+8</f>
+        <v>80</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="0"/>
-        <v>0.12</v>
+        <v>0.13333333333333333</v>
       </c>
       <c r="J8" s="11">
         <v>575</v>
       </c>
       <c r="K8" s="12">
-        <f>14.1+13+0+46+23+10+12+20</f>
-        <v>138.1</v>
+        <f>14.1+13+0+46+23+10+12+20+11</f>
+        <v>149.1</v>
       </c>
       <c r="L8" s="71">
         <f t="shared" si="1"/>
-        <v>0.24017391304347824</v>
+        <v>0.25930434782608697</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>436.9</v>
+        <v>425.9</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>25.7</v>
+        <v>26.618749999999999</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
-        <v>1.9180555555555554</v>
+        <v>1.86375</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>2.0014492753623188</v>
+        <v>1.9447826086956523</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -3982,7 +3980,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>32.352941176470587</v>
+        <v>34.375</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4017,39 +4015,39 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <f>4+7+3+3+3</f>
-        <v>20</v>
+        <f>4+7+3+3+3+6</f>
+        <v>26</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="J10" s="11">
         <v>4620</v>
       </c>
       <c r="K10" s="12">
-        <f>70+42+31+40+23</f>
-        <v>206</v>
+        <f>70+42+31+40+23+74</f>
+        <v>280</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>4.4588744588744587E-2</v>
+        <v>6.0606060606060608E-2</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>4414</v>
+        <v>4340</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>259.64705882352939</v>
+        <v>271.25</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>10.3</v>
+        <v>10.76923076923077</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>0.44588744588744583</v>
+        <v>0.46620046620046618</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4100,7 +4098,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>37.176470588235297</v>
+        <v>39.5</v>
       </c>
       <c r="O11" s="72">
         <f t="shared" si="4"/>
@@ -4157,7 +4155,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>31.235294117647058</v>
+        <v>33.1875</v>
       </c>
       <c r="O12" s="72">
         <f t="shared" si="4"/>
@@ -4357,7 +4355,7 @@
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>70.588235294117652</v>
+        <v>75</v>
       </c>
       <c r="O16" s="72">
         <f t="shared" si="10"/>
@@ -4464,11 +4462,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>6.3E-2</v>
+        <v>6.7199999999999996E-2</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4476,23 +4474,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>896.3</v>
+        <v>988.3</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>8.4001874414245545E-2</v>
+        <v>9.2624179943767565E-2</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>9773.7000000000007</v>
+        <v>9681.7000000000007</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>574.92352941176478</v>
+        <v>605.10625000000005</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>2.8453968253968251</v>
+        <v>2.9413690476190473</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4545,7 +4543,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>27.352941176470587</v>
+        <v>29.0625</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4601,7 +4599,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>27.470588235294116</v>
+        <v>29.1875</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4657,7 +4655,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>27.294117647058822</v>
+        <v>29</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4713,7 +4711,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>27.823529411764707</v>
+        <v>29.5625</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4769,7 +4767,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>28.470588235294116</v>
+        <v>30.25</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4825,7 +4823,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>138.41176470588235</v>
+        <v>147.0625</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4882,7 +4880,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>36.235294117647058</v>
+        <v>38.5</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -4938,7 +4936,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>33.294117647058826</v>
+        <v>35.375</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -4994,7 +4992,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>33.764705882352942</v>
+        <v>35.875</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5050,7 +5048,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>36</v>
+        <v>38.25</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5106,7 +5104,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>139.29411764705881</v>
+        <v>148</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5135,11 +5133,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>516</v>
+        <v>537</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>9.467889908256881E-2</v>
+        <v>9.8532110091743119E-2</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5147,23 +5145,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>1175.3</v>
+        <v>1267.3</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>7.5003190810465858E-2</v>
+        <v>8.0874282067645173E-2</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>14494.7</v>
+        <v>14402.7</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>852.62941176470588</v>
+        <v>900.16875000000005</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>2.2777131782945736</v>
+        <v>2.3599627560521412</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/july 2026/Daily Reports/Sales Reporting PPL - Rana Bilal Lahore (Final).xlsx
+++ b/july 2026/Daily Reports/Sales Reporting PPL - Rana Bilal Lahore (Final).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99C14041-1360-46A5-BEBA-529BCC44EFB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56162CD1-FBDE-4357-A65D-B9AF8E5EAB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="76">
   <si>
     <t>Booking</t>
   </si>
@@ -250,10 +250,10 @@
     <t>Hamid</t>
   </si>
   <si>
-    <t>On Leave</t>
-  </si>
-  <si>
     <t>Resignd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leave </t>
   </si>
 </sst>
 </file>
@@ -1545,7 +1545,7 @@
     </row>
     <row r="2" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="94">
-        <v>46214</v>
+        <v>46216</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>2</v>
@@ -1666,57 +1666,57 @@
         <v>50</v>
       </c>
       <c r="H4" s="8">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I4" s="32">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.16</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="J4" s="30">
         <v>40</v>
       </c>
       <c r="K4" s="31">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L4" s="32">
         <f t="shared" ref="L4:L12" si="1">K4/J4</f>
-        <v>0.52500000000000002</v>
+        <v>0.375</v>
       </c>
       <c r="M4" s="30">
         <f t="shared" ref="M4:N12" si="2">K4/H4</f>
-        <v>2.625</v>
+        <v>1.0714285714285714</v>
       </c>
       <c r="N4" s="33">
         <f t="shared" si="2"/>
-        <v>3.28125</v>
+        <v>1.3392857142857142</v>
       </c>
       <c r="O4" s="30">
         <v>12</v>
       </c>
       <c r="P4" s="96">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q4" s="32">
         <f t="shared" ref="Q4:Q12" si="3">P4/O4</f>
-        <v>0.91666666666666663</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="R4" s="30">
         <v>8</v>
       </c>
       <c r="S4" s="96">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="T4" s="32">
         <f t="shared" ref="T4:T12" si="4">S4/R4</f>
-        <v>0.875</v>
+        <v>2.625</v>
       </c>
       <c r="U4" s="30">
         <f t="shared" ref="U4:V12" si="5">S4/P4</f>
-        <v>0.63636363636363635</v>
+        <v>2.625</v>
       </c>
       <c r="V4" s="33">
         <f t="shared" si="5"/>
-        <v>0.95454545454545459</v>
+        <v>3.9375</v>
       </c>
       <c r="W4" s="34"/>
     </row>
@@ -1742,56 +1742,58 @@
       <c r="G5" s="30">
         <v>50</v>
       </c>
-      <c r="H5" s="12"/>
+      <c r="H5" s="12">
+        <v>7</v>
+      </c>
       <c r="I5" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="J5" s="30">
         <v>30</v>
       </c>
-      <c r="K5" s="12"/>
+      <c r="K5" s="12">
+        <v>11</v>
+      </c>
       <c r="L5" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M5" s="11" t="e">
+        <v>0.36666666666666664</v>
+      </c>
+      <c r="M5" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N5" s="14" t="e">
+        <v>1.5714285714285714</v>
+      </c>
+      <c r="N5" s="14">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>2.6190476190476186</v>
       </c>
       <c r="O5" s="30">
         <v>7</v>
       </c>
-      <c r="P5" s="97">
-        <v>14</v>
-      </c>
+      <c r="P5" s="97"/>
       <c r="Q5" s="13">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R5" s="30">
         <v>13</v>
       </c>
-      <c r="S5" s="97">
-        <v>17</v>
-      </c>
+      <c r="S5" s="97"/>
       <c r="T5" s="13">
         <f t="shared" si="4"/>
-        <v>1.3076923076923077</v>
-      </c>
-      <c r="U5" s="11">
+        <v>0</v>
+      </c>
+      <c r="U5" s="11" t="e">
         <f t="shared" si="5"/>
-        <v>1.2142857142857142</v>
-      </c>
-      <c r="V5" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V5" s="14" t="e">
         <f t="shared" si="5"/>
-        <v>0.65384615384615385</v>
-      </c>
-      <c r="W5" s="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W5" s="34" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="6" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="35" t="s">
@@ -1861,7 +1863,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="W6" s="34" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.5">
@@ -1886,26 +1888,30 @@
       <c r="G7" s="30">
         <v>50</v>
       </c>
-      <c r="H7" s="12"/>
+      <c r="H7" s="12">
+        <v>9</v>
+      </c>
       <c r="I7" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="J7" s="30">
         <v>30</v>
       </c>
-      <c r="K7" s="12"/>
+      <c r="K7" s="12">
+        <v>7</v>
+      </c>
       <c r="L7" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M7" s="11" t="e">
+        <v>0.23333333333333334</v>
+      </c>
+      <c r="M7" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N7" s="14" t="e">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="N7" s="14">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>1.2962962962962963</v>
       </c>
       <c r="O7" s="30">
         <v>5</v>
@@ -1932,7 +1938,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="W7" s="34" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.5">
@@ -1958,57 +1964,57 @@
         <v>50</v>
       </c>
       <c r="H8" s="12">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I8" s="13">
         <f t="shared" si="0"/>
-        <v>0.16</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="J8" s="30">
         <v>20</v>
       </c>
       <c r="K8" s="12">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L8" s="13">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="M8" s="11">
         <f t="shared" si="2"/>
-        <v>1.875</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="2"/>
-        <v>4.6875</v>
+        <v>2.1428571428571428</v>
       </c>
       <c r="O8" s="30">
         <v>15</v>
       </c>
       <c r="P8" s="97">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q8" s="13">
         <f t="shared" si="3"/>
-        <v>0.46666666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="R8" s="30">
         <v>15</v>
       </c>
       <c r="S8" s="97">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T8" s="13">
         <f t="shared" si="4"/>
-        <v>0.93333333333333335</v>
+        <v>1.0666666666666667</v>
       </c>
       <c r="U8" s="11">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1.7777777777777777</v>
       </c>
       <c r="V8" s="14">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1.7777777777777779</v>
       </c>
       <c r="W8" s="34"/>
     </row>
@@ -2103,17 +2109,17 @@
         <v>25</v>
       </c>
       <c r="H10" s="12">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I10" s="13">
         <f t="shared" si="0"/>
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="J10" s="30">
         <v>0</v>
       </c>
       <c r="K10" s="12">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="L10" s="13" t="e">
         <f t="shared" si="1"/>
@@ -2121,7 +2127,7 @@
       </c>
       <c r="M10" s="11">
         <f t="shared" si="2"/>
-        <v>8.5</v>
+        <v>35</v>
       </c>
       <c r="N10" s="14" t="e">
         <f t="shared" si="2"/>
@@ -2129,18 +2135,18 @@
       </c>
       <c r="O10" s="30">
         <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="P10" s="97">
         <v>6</v>
-      </c>
-      <c r="P10" s="97">
-        <v>5</v>
       </c>
       <c r="Q10" s="13">
         <f t="shared" si="3"/>
-        <v>0.83333333333333337</v>
+        <v>6</v>
       </c>
       <c r="R10" s="30"/>
       <c r="S10" s="97">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="T10" s="13" t="e">
         <f t="shared" si="4"/>
@@ -2148,7 +2154,7 @@
       </c>
       <c r="U10" s="11">
         <f t="shared" si="5"/>
-        <v>14.8</v>
+        <v>8.1666666666666661</v>
       </c>
       <c r="V10" s="14" t="e">
         <f t="shared" si="5"/>
@@ -2531,11 +2537,11 @@
       </c>
       <c r="H19" s="41">
         <f>SUM(H4:H18)</f>
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="I19" s="42">
         <f t="shared" si="0"/>
-        <v>5.8666666666666666E-2</v>
+        <v>0.12</v>
       </c>
       <c r="J19" s="40">
         <f>SUM(J4:J18)</f>
@@ -2543,15 +2549,15 @@
       </c>
       <c r="K19" s="41">
         <f>SUM(K4:K18)</f>
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="L19" s="42">
         <f t="shared" ref="L19" si="7">K19/J19</f>
-        <v>0.22597402597402597</v>
+        <v>0.20779220779220781</v>
       </c>
       <c r="M19" s="40">
         <f>K19/H19</f>
-        <v>3.9545454545454546</v>
+        <v>1.7777777777777777</v>
       </c>
       <c r="N19" s="43" t="e">
         <f>AVERAGE(N4:N18)</f>
@@ -2559,15 +2565,15 @@
       </c>
       <c r="O19" s="40">
         <f>SUM(O4:O18)</f>
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="P19" s="41">
         <f>SUM(P4:P18)</f>
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="Q19" s="42">
         <f t="shared" ref="Q19" si="8">P19/O19</f>
-        <v>0.69811320754716977</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="R19" s="40">
         <f>SUM(R4:R18)</f>
@@ -2575,15 +2581,15 @@
       </c>
       <c r="S19" s="41">
         <f>SUM(S4:S18)</f>
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="T19" s="42">
         <f t="shared" ref="T19" si="9">S19/R19</f>
-        <v>2.7317073170731709</v>
+        <v>2.0975609756097562</v>
       </c>
       <c r="U19" s="40">
         <f>S19/P19</f>
-        <v>3.0270270270270272</v>
+        <v>3.7391304347826089</v>
       </c>
       <c r="V19" s="43" t="e">
         <f>AVERAGE(V4:V18)</f>
@@ -3445,11 +3451,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31" si="25">+H30+H25+H19</f>
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="I31" s="22">
         <f t="shared" si="0"/>
-        <v>5.2892561983471073E-2</v>
+        <v>6.0495867768595044E-2</v>
       </c>
       <c r="J31" s="20">
         <f>+J30+J25+J19</f>
@@ -3457,15 +3463,15 @@
       </c>
       <c r="K31" s="21">
         <f t="shared" ref="K31" si="26">+K30+K25+K19</f>
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="L31" s="22">
         <f t="shared" si="10"/>
-        <v>9.8259187620889754E-2</v>
+        <v>9.5551257253384911E-2</v>
       </c>
       <c r="M31" s="20">
         <f>K31/H31</f>
-        <v>1.5874999999999999</v>
+        <v>1.3497267759562841</v>
       </c>
       <c r="N31" s="23" t="e">
         <f>AVERAGE(N30,N19,N25)</f>
@@ -3473,15 +3479,15 @@
       </c>
       <c r="O31" s="20">
         <f>+O30+O25+O19</f>
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="P31" s="21">
         <f t="shared" ref="P31" si="27">+P30+P25+P19</f>
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="Q31" s="22">
         <f t="shared" si="12"/>
-        <v>0.74257425742574257</v>
+        <v>0.69035532994923854</v>
       </c>
       <c r="R31" s="20">
         <f>+R30+R25+R19</f>
@@ -3489,15 +3495,15 @@
       </c>
       <c r="S31" s="21">
         <f t="shared" ref="S31" si="28">+S30+S25+S19</f>
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="T31" s="22">
         <f t="shared" si="13"/>
-        <v>0.86428571428571432</v>
+        <v>0.77142857142857146</v>
       </c>
       <c r="U31" s="20">
         <f>S31/P31</f>
-        <v>1.6133333333333333</v>
+        <v>1.588235294117647</v>
       </c>
       <c r="V31" s="23" t="e">
         <f>AVERAGE(V30,V19,V25)</f>
@@ -3562,18 +3568,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.40740740740740738</v>
+        <v>0.48148148148148145</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F2" s="94">
-        <v>46214</v>
+        <v>46216</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>40</v>
@@ -3668,35 +3674,35 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>5+9+9+11+10+9+11+8</f>
-        <v>72</v>
+        <f>5+9+9+11+10+9+11+8+11</f>
+        <v>83</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.12</v>
+        <v>0.13833333333333334</v>
       </c>
       <c r="J4" s="30">
         <v>575</v>
       </c>
       <c r="K4" s="8">
-        <f>8.5+9+12+11+17+6+12+14</f>
-        <v>89.5</v>
+        <f>8.5+9+12+11+17+6+12+14+7</f>
+        <v>96.5</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.15565217391304348</v>
+        <v>0.16782608695652174</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>485.5</v>
+        <v>478.5</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>30.34375</v>
+        <v>34.178571428571431</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.2430555555555556</v>
+        <v>1.1626506024096386</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3726,39 +3732,39 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>4+8+7+17+7+3+2+5+7</f>
-        <v>60</v>
+        <f>4+8+7+17+7+3+2+5+7+14</f>
+        <v>74</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.12333333333333334</v>
       </c>
       <c r="J5" s="11">
         <v>550</v>
       </c>
       <c r="K5" s="12">
-        <f>6.6+9+5+6+11+4+6+7</f>
-        <v>54.6</v>
+        <f>6.6+9+5+6+11+4+6+7+17</f>
+        <v>71.599999999999994</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>9.9272727272727276E-2</v>
+        <v>0.13018181818181818</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>495.4</v>
+        <v>478.4</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>30.962499999999999</v>
+        <v>34.171428571428571</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>0.91</v>
+        <v>0.96756756756756745</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>0.99272727272727268</v>
+        <v>1.0555282555282555</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3809,7 +3815,7 @@
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>31.5</v>
+        <v>36</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
@@ -3868,7 +3874,7 @@
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>32.368749999999999</v>
+        <v>36.99285714285714</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
@@ -3903,39 +3909,39 @@
         <v>600</v>
       </c>
       <c r="H8" s="12">
-        <f>10+10+0+14+6+10+11+11+8</f>
-        <v>80</v>
+        <f>10+10+0+14+6+10+11+11+8+7</f>
+        <v>87</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="0"/>
-        <v>0.13333333333333333</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="J8" s="11">
         <v>575</v>
       </c>
       <c r="K8" s="12">
-        <f>14.1+13+0+46+23+10+12+20+11</f>
-        <v>149.1</v>
+        <f>14.1+13+0+46+23+10+12+20+11+14</f>
+        <v>163.1</v>
       </c>
       <c r="L8" s="71">
         <f t="shared" si="1"/>
-        <v>0.25930434782608697</v>
+        <v>0.28365217391304348</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>425.9</v>
+        <v>411.9</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>26.618749999999999</v>
+        <v>29.421428571428571</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
-        <v>1.86375</v>
+        <v>1.8747126436781609</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>1.9447826086956523</v>
+        <v>1.9562218890554723</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -3980,7 +3986,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>34.375</v>
+        <v>39.285714285714285</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4015,39 +4021,39 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <f>4+7+3+3+3+6</f>
-        <v>26</v>
+        <f>4+7+3+3+3+6+5</f>
+        <v>31</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>0.13</v>
+        <v>0.155</v>
       </c>
       <c r="J10" s="11">
         <v>4620</v>
       </c>
       <c r="K10" s="12">
-        <f>70+42+31+40+23+74</f>
-        <v>280</v>
+        <f>70+42+31+40+23+74+74</f>
+        <v>354</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>6.0606060606060608E-2</v>
+        <v>7.6623376623376621E-2</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>4340</v>
+        <v>4266</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>271.25</v>
+        <v>304.71428571428572</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>10.76923076923077</v>
+        <v>11.419354838709678</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>0.46620046620046618</v>
+        <v>0.49434436531210724</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4098,7 +4104,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>39.5</v>
+        <v>45.142857142857146</v>
       </c>
       <c r="O11" s="72">
         <f t="shared" si="4"/>
@@ -4155,7 +4161,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>33.1875</v>
+        <v>37.928571428571431</v>
       </c>
       <c r="O12" s="72">
         <f t="shared" si="4"/>
@@ -4355,7 +4361,7 @@
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>75</v>
+        <v>85.714285714285708</v>
       </c>
       <c r="O16" s="72">
         <f t="shared" si="10"/>
@@ -4462,11 +4468,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>336</v>
+        <v>373</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>6.7199999999999996E-2</v>
+        <v>7.46E-2</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4474,23 +4480,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>988.3</v>
+        <v>1100.3</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>9.2624179943767565E-2</v>
+        <v>0.10312089971883785</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>9681.7000000000007</v>
+        <v>9569.7000000000007</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>605.10625000000005</v>
+        <v>683.55000000000007</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>2.9413690476190473</v>
+        <v>2.9498659517426273</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4543,7 +4549,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>29.0625</v>
+        <v>33.214285714285715</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4599,7 +4605,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>29.1875</v>
+        <v>33.357142857142854</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4655,7 +4661,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>33.142857142857146</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4711,7 +4717,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>29.5625</v>
+        <v>33.785714285714285</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4767,7 +4773,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>30.25</v>
+        <v>34.571428571428569</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4823,7 +4829,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>147.0625</v>
+        <v>168.07142857142858</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4880,7 +4886,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>38.5</v>
+        <v>44</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -4936,7 +4942,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>35.375</v>
+        <v>40.428571428571431</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -4992,7 +4998,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>35.875</v>
+        <v>41</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5048,7 +5054,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>38.25</v>
+        <v>43.714285714285715</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5104,7 +5110,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>148</v>
+        <v>169.14285714285714</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5133,11 +5139,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>537</v>
+        <v>574</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>9.8532110091743119E-2</v>
+        <v>0.10532110091743119</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5145,23 +5151,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>1267.3</v>
+        <v>1379.3</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>8.0874282067645173E-2</v>
+        <v>8.802169751116784E-2</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>14402.7</v>
+        <v>14290.7</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>900.16875000000005</v>
+        <v>1020.7642857142857</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>2.3599627560521412</v>
+        <v>2.4029616724738676</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/july 2026/Daily Reports/Sales Reporting PPL - Rana Bilal Lahore (Final).xlsx
+++ b/july 2026/Daily Reports/Sales Reporting PPL - Rana Bilal Lahore (Final).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56162CD1-FBDE-4357-A65D-B9AF8E5EAB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFAE29B-F8AE-4D25-98B2-E5D8271DADD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="75">
   <si>
     <t>Booking</t>
   </si>
@@ -251,9 +251,6 @@
   </si>
   <si>
     <t>Resignd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leave </t>
   </si>
 </sst>
 </file>
@@ -1545,7 +1542,7 @@
     </row>
     <row r="2" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="94">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>2</v>
@@ -1666,57 +1663,57 @@
         <v>50</v>
       </c>
       <c r="H4" s="8">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I4" s="32">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.28000000000000003</v>
+        <v>0.24</v>
       </c>
       <c r="J4" s="30">
         <v>40</v>
       </c>
       <c r="K4" s="31">
-        <v>15</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="L4" s="32">
         <f t="shared" ref="L4:L12" si="1">K4/J4</f>
-        <v>0.375</v>
+        <v>0.22000000000000003</v>
       </c>
       <c r="M4" s="30">
         <f t="shared" ref="M4:N12" si="2">K4/H4</f>
-        <v>1.0714285714285714</v>
+        <v>0.73333333333333339</v>
       </c>
       <c r="N4" s="33">
         <f t="shared" si="2"/>
-        <v>1.3392857142857142</v>
+        <v>0.91666666666666685</v>
       </c>
       <c r="O4" s="30">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P4" s="96">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Q4" s="32">
         <f t="shared" ref="Q4:Q12" si="3">P4/O4</f>
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="R4" s="30">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="S4" s="96">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="T4" s="32">
         <f t="shared" ref="T4:T12" si="4">S4/R4</f>
-        <v>2.625</v>
+        <v>0.96666666666666667</v>
       </c>
       <c r="U4" s="30">
         <f t="shared" ref="U4:V12" si="5">S4/P4</f>
-        <v>2.625</v>
+        <v>1.0357142857142858</v>
       </c>
       <c r="V4" s="33">
         <f t="shared" si="5"/>
-        <v>3.9375</v>
+        <v>0.96666666666666667</v>
       </c>
       <c r="W4" s="34"/>
     </row>
@@ -1743,57 +1740,59 @@
         <v>50</v>
       </c>
       <c r="H5" s="12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I5" s="13">
         <f t="shared" si="0"/>
-        <v>0.14000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="J5" s="30">
         <v>30</v>
       </c>
       <c r="K5" s="12">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L5" s="13">
         <f t="shared" si="1"/>
-        <v>0.36666666666666664</v>
+        <v>0.5</v>
       </c>
       <c r="M5" s="11">
         <f t="shared" si="2"/>
-        <v>1.5714285714285714</v>
+        <v>2.5</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="2"/>
-        <v>2.6190476190476186</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="O5" s="30">
         <v>7</v>
       </c>
-      <c r="P5" s="97"/>
+      <c r="P5" s="97">
+        <v>6</v>
+      </c>
       <c r="Q5" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="R5" s="30">
-        <v>13</v>
-      </c>
-      <c r="S5" s="97"/>
+        <v>11</v>
+      </c>
+      <c r="S5" s="97">
+        <v>9.8000000000000007</v>
+      </c>
       <c r="T5" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U5" s="11" t="e">
+        <v>0.89090909090909098</v>
+      </c>
+      <c r="U5" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V5" s="14" t="e">
+        <v>1.6333333333333335</v>
+      </c>
+      <c r="V5" s="14">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W5" s="34" t="s">
-        <v>75</v>
-      </c>
+        <v>1.0393939393939395</v>
+      </c>
+      <c r="W5" s="34"/>
     </row>
     <row r="6" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A6" s="35" t="s">
@@ -1889,57 +1888,59 @@
         <v>50</v>
       </c>
       <c r="H7" s="12">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I7" s="13">
         <f t="shared" si="0"/>
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="J7" s="30">
         <v>30</v>
       </c>
       <c r="K7" s="12">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L7" s="13">
         <f t="shared" si="1"/>
-        <v>0.23333333333333334</v>
+        <v>0.36666666666666664</v>
       </c>
       <c r="M7" s="11">
         <f t="shared" si="2"/>
-        <v>0.77777777777777779</v>
+        <v>1.8333333333333333</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" si="2"/>
-        <v>1.2962962962962963</v>
+        <v>3.0555555555555554</v>
       </c>
       <c r="O7" s="30">
-        <v>5</v>
-      </c>
-      <c r="P7" s="97"/>
+        <v>9</v>
+      </c>
+      <c r="P7" s="97">
+        <v>9</v>
+      </c>
       <c r="Q7" s="13">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" s="30">
-        <v>5</v>
-      </c>
-      <c r="S7" s="97"/>
+        <v>7</v>
+      </c>
+      <c r="S7" s="97">
+        <v>6.7</v>
+      </c>
       <c r="T7" s="13">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U7" s="11" t="e">
+        <v>0.95714285714285718</v>
+      </c>
+      <c r="U7" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V7" s="14" t="e">
+        <v>0.74444444444444446</v>
+      </c>
+      <c r="V7" s="14">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W7" s="34" t="s">
-        <v>75</v>
-      </c>
+        <v>0.95714285714285718</v>
+      </c>
+      <c r="W7" s="34"/>
     </row>
     <row r="8" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="35" t="s">
@@ -1964,57 +1965,57 @@
         <v>50</v>
       </c>
       <c r="H8" s="12">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I8" s="13">
         <f t="shared" si="0"/>
-        <v>0.28000000000000003</v>
+        <v>0.16</v>
       </c>
       <c r="J8" s="30">
         <v>20</v>
       </c>
       <c r="K8" s="12">
-        <v>12</v>
+        <v>5.3</v>
       </c>
       <c r="L8" s="13">
         <f t="shared" si="1"/>
-        <v>0.6</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="M8" s="11">
         <f t="shared" si="2"/>
-        <v>0.8571428571428571</v>
+        <v>0.66249999999999998</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="2"/>
-        <v>2.1428571428571428</v>
+        <v>1.65625</v>
       </c>
       <c r="O8" s="30">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P8" s="97">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Q8" s="13">
         <f t="shared" si="3"/>
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="R8" s="30">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="S8" s="97">
-        <v>16</v>
+        <v>11.4</v>
       </c>
       <c r="T8" s="13">
         <f t="shared" si="4"/>
-        <v>1.0666666666666667</v>
+        <v>0.95000000000000007</v>
       </c>
       <c r="U8" s="11">
         <f t="shared" si="5"/>
-        <v>1.7777777777777777</v>
+        <v>0.81428571428571428</v>
       </c>
       <c r="V8" s="14">
         <f t="shared" si="5"/>
-        <v>1.7777777777777779</v>
+        <v>0.95000000000000007</v>
       </c>
       <c r="W8" s="34"/>
     </row>
@@ -2062,7 +2063,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O9" s="30">
-        <f t="shared" ref="O9:O10" si="6">H9</f>
+        <f t="shared" ref="O9" si="6">H9</f>
         <v>0</v>
       </c>
       <c r="P9" s="97"/>
@@ -2119,7 +2120,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="12">
-        <v>35</v>
+        <v>150</v>
       </c>
       <c r="L10" s="13" t="e">
         <f t="shared" si="1"/>
@@ -2127,38 +2128,39 @@
       </c>
       <c r="M10" s="11">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>150</v>
       </c>
       <c r="N10" s="14" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O10" s="30">
-        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="P10" s="97">
         <v>1</v>
-      </c>
-      <c r="P10" s="97">
-        <v>6</v>
       </c>
       <c r="Q10" s="13">
         <f t="shared" si="3"/>
-        <v>6</v>
-      </c>
-      <c r="R10" s="30"/>
+        <v>0.5</v>
+      </c>
+      <c r="R10" s="30">
+        <v>70</v>
+      </c>
       <c r="S10" s="97">
-        <v>49</v>
-      </c>
-      <c r="T10" s="13" t="e">
+        <v>35</v>
+      </c>
+      <c r="T10" s="13">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>0.5</v>
       </c>
       <c r="U10" s="11">
         <f t="shared" si="5"/>
-        <v>8.1666666666666661</v>
-      </c>
-      <c r="V10" s="14" t="e">
+        <v>35</v>
+      </c>
+      <c r="V10" s="14">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="W10" s="34"/>
     </row>
@@ -2537,11 +2539,11 @@
       </c>
       <c r="H19" s="41">
         <f>SUM(H4:H18)</f>
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="I19" s="42">
         <f t="shared" si="0"/>
-        <v>0.12</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="J19" s="40">
         <f>SUM(J4:J18)</f>
@@ -2549,15 +2551,15 @@
       </c>
       <c r="K19" s="41">
         <f>SUM(K4:K18)</f>
-        <v>80</v>
+        <v>190.1</v>
       </c>
       <c r="L19" s="42">
         <f t="shared" ref="L19" si="7">K19/J19</f>
-        <v>0.20779220779220781</v>
+        <v>0.49376623376623374</v>
       </c>
       <c r="M19" s="40">
         <f>K19/H19</f>
-        <v>1.7777777777777777</v>
+        <v>5.7606060606060607</v>
       </c>
       <c r="N19" s="43" t="e">
         <f>AVERAGE(N4:N18)</f>
@@ -2565,31 +2567,31 @@
       </c>
       <c r="O19" s="40">
         <f>SUM(O4:O18)</f>
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="P19" s="41">
         <f>SUM(P4:P18)</f>
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="Q19" s="42">
         <f t="shared" ref="Q19" si="8">P19/O19</f>
-        <v>0.47916666666666669</v>
+        <v>0.81481481481481477</v>
       </c>
       <c r="R19" s="40">
         <f>SUM(R4:R18)</f>
-        <v>41</v>
+        <v>115</v>
       </c>
       <c r="S19" s="41">
         <f>SUM(S4:S18)</f>
-        <v>86</v>
+        <v>77.400000000000006</v>
       </c>
       <c r="T19" s="42">
         <f t="shared" ref="T19" si="9">S19/R19</f>
-        <v>2.0975609756097562</v>
+        <v>0.67304347826086963</v>
       </c>
       <c r="U19" s="40">
         <f>S19/P19</f>
-        <v>3.7391304347826089</v>
+        <v>1.7590909090909093</v>
       </c>
       <c r="V19" s="43" t="e">
         <f>AVERAGE(V4:V18)</f>
@@ -3451,11 +3453,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31" si="25">+H30+H25+H19</f>
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="I31" s="22">
         <f t="shared" si="0"/>
-        <v>6.0495867768595044E-2</v>
+        <v>5.6528925619834712E-2</v>
       </c>
       <c r="J31" s="20">
         <f>+J30+J25+J19</f>
@@ -3463,15 +3465,15 @@
       </c>
       <c r="K31" s="21">
         <f t="shared" ref="K31" si="26">+K30+K25+K19</f>
-        <v>247</v>
+        <v>357.1</v>
       </c>
       <c r="L31" s="22">
         <f t="shared" si="10"/>
-        <v>9.5551257253384911E-2</v>
+        <v>0.13814313346228241</v>
       </c>
       <c r="M31" s="20">
         <f>K31/H31</f>
-        <v>1.3497267759562841</v>
+        <v>2.0883040935672517</v>
       </c>
       <c r="N31" s="23" t="e">
         <f>AVERAGE(N30,N19,N25)</f>
@@ -3479,31 +3481,31 @@
       </c>
       <c r="O31" s="20">
         <f>+O30+O25+O19</f>
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="P31" s="21">
         <f t="shared" ref="P31" si="27">+P30+P25+P19</f>
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="Q31" s="22">
         <f t="shared" si="12"/>
-        <v>0.69035532994923854</v>
+        <v>0.77339901477832518</v>
       </c>
       <c r="R31" s="20">
         <f>+R30+R25+R19</f>
-        <v>280</v>
+        <v>354</v>
       </c>
       <c r="S31" s="21">
         <f t="shared" ref="S31" si="28">+S30+S25+S19</f>
-        <v>216</v>
+        <v>207.4</v>
       </c>
       <c r="T31" s="22">
         <f t="shared" si="13"/>
-        <v>0.77142857142857146</v>
+        <v>0.58587570621468932</v>
       </c>
       <c r="U31" s="20">
         <f>S31/P31</f>
-        <v>1.588235294117647</v>
+        <v>1.3210191082802547</v>
       </c>
       <c r="V31" s="23" t="e">
         <f>AVERAGE(V30,V19,V25)</f>
@@ -3568,18 +3570,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.48148148148148145</v>
+        <v>0.51851851851851849</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F2" s="94">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>40</v>
@@ -3674,35 +3676,34 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>5+9+9+11+10+9+11+8+11</f>
-        <v>83</v>
+        <f>5+9+9+11+10+9+11+8+11+8</f>
+        <v>91</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.13833333333333334</v>
+        <v>0.15166666666666667</v>
       </c>
       <c r="J4" s="30">
         <v>575</v>
       </c>
       <c r="K4" s="8">
-        <f>8.5+9+12+11+17+6+12+14+7</f>
-        <v>96.5</v>
+        <v>130.65</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.16782608695652174</v>
+        <v>0.22721739130434784</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>478.5</v>
+        <v>444.35</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>34.178571428571431</v>
+        <v>34.180769230769229</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.1626506024096386</v>
+        <v>1.4357142857142857</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3743,28 +3744,27 @@
         <v>550</v>
       </c>
       <c r="K5" s="12">
-        <f>6.6+9+5+6+11+4+6+7+17</f>
-        <v>71.599999999999994</v>
+        <v>81.52</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>0.13018181818181818</v>
+        <v>0.1482181818181818</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>478.4</v>
+        <v>468.48</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>34.171428571428571</v>
+        <v>36.036923076923081</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>0.96756756756756745</v>
+        <v>1.1016216216216215</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>1.0555282555282555</v>
+        <v>1.2017690417690416</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>36</v>
+        <v>38.769230769230766</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
@@ -3861,28 +3861,27 @@
         <v>550</v>
       </c>
       <c r="K7" s="12">
-        <f>7.1+13+0+5+1+6</f>
-        <v>32.1</v>
+        <v>35.799999999999997</v>
       </c>
       <c r="L7" s="71">
         <f t="shared" si="1"/>
-        <v>5.8363636363636368E-2</v>
+        <v>6.5090909090909088E-2</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" ref="M7:M31" si="5">J7-K7</f>
-        <v>517.9</v>
+        <v>514.20000000000005</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>36.99285714285714</v>
+        <v>39.553846153846159</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
-        <v>1.106896551724138</v>
+        <v>1.2344827586206895</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="4"/>
-        <v>1.207523510971787</v>
+        <v>1.3467084639498432</v>
       </c>
       <c r="Q7" s="34"/>
     </row>
@@ -3909,39 +3908,38 @@
         <v>600</v>
       </c>
       <c r="H8" s="12">
-        <f>10+10+0+14+6+10+11+11+8+7</f>
-        <v>87</v>
+        <f>10+10+0+14+6+10+11+11+8+7+9</f>
+        <v>96</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="0"/>
-        <v>0.14499999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="J8" s="11">
         <v>575</v>
       </c>
       <c r="K8" s="12">
-        <f>14.1+13+0+46+23+10+12+20+11+14</f>
-        <v>163.1</v>
+        <v>215.6</v>
       </c>
       <c r="L8" s="71">
         <f t="shared" si="1"/>
-        <v>0.28365217391304348</v>
+        <v>0.37495652173913041</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>411.9</v>
+        <v>359.4</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>29.421428571428571</v>
+        <v>27.646153846153844</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
-        <v>1.8747126436781609</v>
+        <v>2.2458333333333331</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>1.9562218890554723</v>
+        <v>2.3434782608695652</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -3986,7 +3984,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>39.285714285714285</v>
+        <v>42.307692307692307</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4021,39 +4019,38 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <f>4+7+3+3+3+6+5</f>
-        <v>31</v>
+        <f>4+7+3+3+3+6+5+6</f>
+        <v>37</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>0.155</v>
+        <v>0.185</v>
       </c>
       <c r="J10" s="11">
         <v>4620</v>
       </c>
       <c r="K10" s="12">
-        <f>70+42+31+40+23+74+74</f>
-        <v>354</v>
+        <v>541.87</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>7.6623376623376621E-2</v>
+        <v>0.11728787878787879</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>4266</v>
+        <v>4078.13</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>304.71428571428572</v>
+        <v>313.70230769230773</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>11.419354838709678</v>
+        <v>14.645135135135135</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>0.49434436531210724</v>
+        <v>0.63398853398853405</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4104,7 +4101,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>45.142857142857146</v>
+        <v>48.615384615384613</v>
       </c>
       <c r="O11" s="72">
         <f t="shared" si="4"/>
@@ -4161,7 +4158,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>37.928571428571431</v>
+        <v>40.846153846153847</v>
       </c>
       <c r="O12" s="72">
         <f t="shared" si="4"/>
@@ -4361,7 +4358,7 @@
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>85.714285714285708</v>
+        <v>92.307692307692307</v>
       </c>
       <c r="O16" s="72">
         <f t="shared" si="10"/>
@@ -4468,11 +4465,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>373</v>
+        <v>396</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>7.46E-2</v>
+        <v>7.9200000000000007E-2</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4480,23 +4477,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>1100.3</v>
+        <v>1388.44</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>0.10312089971883785</v>
+        <v>0.13012558575445174</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>9569.7000000000007</v>
+        <v>9281.56</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>683.55000000000007</v>
+        <v>713.96615384615382</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>2.9498659517426273</v>
+        <v>3.5061616161616165</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4549,7 +4546,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>33.214285714285715</v>
+        <v>35.769230769230766</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4605,7 +4602,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>33.357142857142854</v>
+        <v>35.92307692307692</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4661,7 +4658,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>33.142857142857146</v>
+        <v>35.692307692307693</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4717,7 +4714,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>33.785714285714285</v>
+        <v>36.384615384615387</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4773,7 +4770,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>34.571428571428569</v>
+        <v>37.230769230769234</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4829,7 +4826,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>168.07142857142858</v>
+        <v>181</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4886,7 +4883,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>44</v>
+        <v>47.384615384615387</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -4942,7 +4939,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>40.428571428571431</v>
+        <v>43.53846153846154</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -4998,7 +4995,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>41</v>
+        <v>44.153846153846153</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5054,7 +5051,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>43.714285714285715</v>
+        <v>47.07692307692308</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5110,7 +5107,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>169.14285714285714</v>
+        <v>182.15384615384616</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5139,11 +5136,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>574</v>
+        <v>597</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>0.10532110091743119</v>
+        <v>0.10954128440366973</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5151,23 +5148,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>1379.3</v>
+        <v>1667.44</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>8.802169751116784E-2</v>
+        <v>0.10640970006381621</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>14290.7</v>
+        <v>14002.56</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>1020.7642857142857</v>
+        <v>1077.1199999999999</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>2.4029616724738676</v>
+        <v>2.7930318257956448</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/july 2026/Daily Reports/Sales Reporting PPL - Rana Bilal Lahore (Final).xlsx
+++ b/july 2026/Daily Reports/Sales Reporting PPL - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\july 2026\Daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FFAE29B-F8AE-4D25-98B2-E5D8271DADD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16779AE0-E33B-4DAA-B56B-0D0D7EFC4EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="76">
   <si>
     <t>Booking</t>
   </si>
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>Resignd</t>
+  </si>
+  <si>
+    <t>Not Available</t>
   </si>
 </sst>
 </file>
@@ -1503,7 +1506,7 @@
     <col min="3" max="3" width="15.26953125" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="18.26953125" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="23.7265625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.453125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.453125" style="24" customWidth="1"/>
     <col min="8" max="8" width="7.7265625" customWidth="1"/>
     <col min="9" max="9" width="5.54296875" customWidth="1"/>
@@ -1542,7 +1545,7 @@
     </row>
     <row r="2" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="94">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>2</v>
@@ -1673,47 +1676,47 @@
         <v>40</v>
       </c>
       <c r="K4" s="31">
-        <v>8.8000000000000007</v>
+        <v>11.2</v>
       </c>
       <c r="L4" s="32">
         <f t="shared" ref="L4:L12" si="1">K4/J4</f>
-        <v>0.22000000000000003</v>
+        <v>0.27999999999999997</v>
       </c>
       <c r="M4" s="30">
         <f t="shared" ref="M4:N12" si="2">K4/H4</f>
-        <v>0.73333333333333339</v>
+        <v>0.93333333333333324</v>
       </c>
       <c r="N4" s="33">
         <f t="shared" si="2"/>
-        <v>0.91666666666666685</v>
+        <v>1.1666666666666665</v>
       </c>
       <c r="O4" s="30">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P4" s="96">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q4" s="32">
         <f t="shared" ref="Q4:Q12" si="3">P4/O4</f>
-        <v>1</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="R4" s="30">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="S4" s="96">
-        <v>14.5</v>
+        <v>6.55</v>
       </c>
       <c r="T4" s="32">
         <f t="shared" ref="T4:T12" si="4">S4/R4</f>
-        <v>0.96666666666666667</v>
+        <v>0.93571428571428572</v>
       </c>
       <c r="U4" s="30">
         <f t="shared" ref="U4:V12" si="5">S4/P4</f>
-        <v>1.0357142857142858</v>
+        <v>0.65500000000000003</v>
       </c>
       <c r="V4" s="33">
         <f t="shared" si="5"/>
-        <v>0.96666666666666667</v>
+        <v>1.1228571428571428</v>
       </c>
       <c r="W4" s="34"/>
     </row>
@@ -1740,57 +1743,57 @@
         <v>50</v>
       </c>
       <c r="H5" s="12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I5" s="13">
         <f t="shared" si="0"/>
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="J5" s="30">
         <v>30</v>
       </c>
       <c r="K5" s="12">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L5" s="13">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="M5" s="11">
         <f t="shared" si="2"/>
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="2"/>
-        <v>4.166666666666667</v>
+        <v>2.083333333333333</v>
       </c>
       <c r="O5" s="30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P5" s="97">
         <v>6</v>
       </c>
       <c r="Q5" s="13">
         <f t="shared" si="3"/>
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="R5" s="30">
-        <v>11</v>
+        <v>14.75</v>
       </c>
       <c r="S5" s="97">
-        <v>9.8000000000000007</v>
+        <v>14.75</v>
       </c>
       <c r="T5" s="13">
         <f t="shared" si="4"/>
-        <v>0.89090909090909098</v>
+        <v>1</v>
       </c>
       <c r="U5" s="11">
         <f t="shared" si="5"/>
-        <v>1.6333333333333335</v>
+        <v>2.4583333333333335</v>
       </c>
       <c r="V5" s="14">
         <f t="shared" si="5"/>
-        <v>1.0393939393939395</v>
+        <v>1</v>
       </c>
       <c r="W5" s="34"/>
     </row>
@@ -1816,38 +1819,38 @@
       <c r="G6" s="30">
         <v>50</v>
       </c>
-      <c r="H6" s="12"/>
+      <c r="H6" s="12">
+        <v>5</v>
+      </c>
       <c r="I6" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J6" s="30">
         <v>25</v>
       </c>
-      <c r="K6" s="12"/>
+      <c r="K6" s="12">
+        <v>9</v>
+      </c>
       <c r="L6" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M6" s="11" t="e">
+        <v>0.36</v>
+      </c>
+      <c r="M6" s="11">
         <f t="shared" si="2"/>
+        <v>1.8</v>
+      </c>
+      <c r="N6" s="14">
+        <f t="shared" si="2"/>
+        <v>3.5999999999999996</v>
+      </c>
+      <c r="O6" s="30"/>
+      <c r="P6" s="97"/>
+      <c r="Q6" s="13" t="e">
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N6" s="14" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O6" s="30">
-        <v>8</v>
-      </c>
-      <c r="P6" s="97"/>
-      <c r="Q6" s="13">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="R6" s="30">
-        <v>0</v>
-      </c>
+      <c r="R6" s="30"/>
       <c r="S6" s="97"/>
       <c r="T6" s="13" t="e">
         <f t="shared" si="4"/>
@@ -1887,58 +1890,54 @@
       <c r="G7" s="30">
         <v>50</v>
       </c>
-      <c r="H7" s="12">
-        <v>6</v>
-      </c>
+      <c r="H7" s="12"/>
       <c r="I7" s="13">
         <f t="shared" si="0"/>
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="J7" s="30">
         <v>30</v>
       </c>
-      <c r="K7" s="12">
-        <v>11</v>
-      </c>
+      <c r="K7" s="12"/>
       <c r="L7" s="13">
         <f t="shared" si="1"/>
-        <v>0.36666666666666664</v>
-      </c>
-      <c r="M7" s="11">
+        <v>0</v>
+      </c>
+      <c r="M7" s="11" t="e">
         <f t="shared" si="2"/>
-        <v>1.8333333333333333</v>
-      </c>
-      <c r="N7" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N7" s="14" t="e">
         <f t="shared" si="2"/>
-        <v>3.0555555555555554</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O7" s="30">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P7" s="97">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q7" s="13">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R7" s="30">
-        <v>7</v>
+        <v>10.97</v>
       </c>
       <c r="S7" s="97">
-        <v>6.7</v>
+        <v>10.97</v>
       </c>
       <c r="T7" s="13">
         <f t="shared" si="4"/>
-        <v>0.95714285714285718</v>
+        <v>1</v>
       </c>
       <c r="U7" s="11">
         <f t="shared" si="5"/>
-        <v>0.74444444444444446</v>
+        <v>1.8283333333333334</v>
       </c>
       <c r="V7" s="14">
         <f t="shared" si="5"/>
-        <v>0.95714285714285718</v>
+        <v>1</v>
       </c>
       <c r="W7" s="34"/>
     </row>
@@ -1964,58 +1963,54 @@
       <c r="G8" s="30">
         <v>50</v>
       </c>
-      <c r="H8" s="12">
-        <v>8</v>
-      </c>
+      <c r="H8" s="12"/>
       <c r="I8" s="13">
         <f t="shared" si="0"/>
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="J8" s="30">
         <v>20</v>
       </c>
-      <c r="K8" s="12">
-        <v>5.3</v>
-      </c>
+      <c r="K8" s="12"/>
       <c r="L8" s="13">
         <f t="shared" si="1"/>
-        <v>0.26500000000000001</v>
-      </c>
-      <c r="M8" s="11">
+        <v>0</v>
+      </c>
+      <c r="M8" s="11" t="e">
         <f t="shared" si="2"/>
-        <v>0.66249999999999998</v>
-      </c>
-      <c r="N8" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N8" s="14" t="e">
         <f t="shared" si="2"/>
-        <v>1.65625</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O8" s="30">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="P8" s="97">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Q8" s="13">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R8" s="30">
-        <v>12</v>
+        <v>5.35</v>
       </c>
       <c r="S8" s="97">
-        <v>11.4</v>
+        <v>5.35</v>
       </c>
       <c r="T8" s="13">
         <f t="shared" si="4"/>
-        <v>0.95000000000000007</v>
+        <v>1</v>
       </c>
       <c r="U8" s="11">
         <f t="shared" si="5"/>
-        <v>0.81428571428571428</v>
+        <v>0.66874999999999996</v>
       </c>
       <c r="V8" s="14">
         <f t="shared" si="5"/>
-        <v>0.95000000000000007</v>
+        <v>1</v>
       </c>
       <c r="W8" s="34"/>
     </row>
@@ -2062,10 +2057,7 @@
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O9" s="30">
-        <f t="shared" ref="O9" si="6">H9</f>
-        <v>0</v>
-      </c>
+      <c r="O9" s="30"/>
       <c r="P9" s="97"/>
       <c r="Q9" s="13" t="e">
         <f t="shared" si="3"/>
@@ -2085,7 +2077,9 @@
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W9" s="34"/>
+      <c r="W9" s="34" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="10" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="35" t="s">
@@ -2120,7 +2114,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="12">
-        <v>150</v>
+        <v>4</v>
       </c>
       <c r="L10" s="13" t="e">
         <f t="shared" si="1"/>
@@ -2128,39 +2122,39 @@
       </c>
       <c r="M10" s="11">
         <f t="shared" si="2"/>
-        <v>150</v>
+        <v>4</v>
       </c>
       <c r="N10" s="14" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O10" s="30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P10" s="97">
         <v>1</v>
       </c>
       <c r="Q10" s="13">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="R10" s="30">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="S10" s="97">
-        <v>35</v>
+        <v>125</v>
       </c>
       <c r="T10" s="13">
         <f t="shared" si="4"/>
-        <v>0.5</v>
+        <v>1.0245901639344261</v>
       </c>
       <c r="U10" s="11">
         <f t="shared" si="5"/>
-        <v>35</v>
+        <v>125</v>
       </c>
       <c r="V10" s="14">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>1.0245901639344261</v>
       </c>
       <c r="W10" s="34"/>
     </row>
@@ -2207,9 +2201,7 @@
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O11" s="30">
-        <v>0</v>
-      </c>
+      <c r="O11" s="30"/>
       <c r="P11" s="12"/>
       <c r="Q11" s="13" t="e">
         <f t="shared" si="3"/>
@@ -2253,30 +2245,32 @@
       <c r="G12" s="30">
         <v>50</v>
       </c>
-      <c r="H12" s="12"/>
+      <c r="H12" s="12">
+        <v>14</v>
+      </c>
       <c r="I12" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="J12" s="30">
         <v>20</v>
       </c>
-      <c r="K12" s="12"/>
+      <c r="K12" s="12">
+        <v>7</v>
+      </c>
       <c r="L12" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M12" s="11" t="e">
+        <v>0.35</v>
+      </c>
+      <c r="M12" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N12" s="14" t="e">
+        <v>0.5</v>
+      </c>
+      <c r="N12" s="14">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O12" s="30">
-        <v>0</v>
-      </c>
+        <v>1.2499999999999998</v>
+      </c>
+      <c r="O12" s="30"/>
       <c r="P12" s="12"/>
       <c r="Q12" s="13" t="e">
         <f t="shared" si="3"/>
@@ -2539,11 +2533,11 @@
       </c>
       <c r="H19" s="41">
         <f>SUM(H4:H18)</f>
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I19" s="42">
         <f t="shared" si="0"/>
-        <v>8.7999999999999995E-2</v>
+        <v>0.10666666666666667</v>
       </c>
       <c r="J19" s="40">
         <f>SUM(J4:J18)</f>
@@ -2551,15 +2545,15 @@
       </c>
       <c r="K19" s="41">
         <f>SUM(K4:K18)</f>
-        <v>190.1</v>
+        <v>41.2</v>
       </c>
       <c r="L19" s="42">
-        <f t="shared" ref="L19" si="7">K19/J19</f>
-        <v>0.49376623376623374</v>
+        <f t="shared" ref="L19" si="6">K19/J19</f>
+        <v>0.10701298701298702</v>
       </c>
       <c r="M19" s="40">
         <f>K19/H19</f>
-        <v>5.7606060606060607</v>
+        <v>1.03</v>
       </c>
       <c r="N19" s="43" t="e">
         <f>AVERAGE(N4:N18)</f>
@@ -2567,31 +2561,31 @@
       </c>
       <c r="O19" s="40">
         <f>SUM(O4:O18)</f>
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="P19" s="41">
         <f>SUM(P4:P18)</f>
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="Q19" s="42">
-        <f t="shared" ref="Q19" si="8">P19/O19</f>
-        <v>0.81481481481481477</v>
+        <f t="shared" ref="Q19" si="7">P19/O19</f>
+        <v>0.93939393939393945</v>
       </c>
       <c r="R19" s="40">
         <f>SUM(R4:R18)</f>
-        <v>115</v>
+        <v>160.07</v>
       </c>
       <c r="S19" s="41">
         <f>SUM(S4:S18)</f>
-        <v>77.400000000000006</v>
+        <v>162.62</v>
       </c>
       <c r="T19" s="42">
-        <f t="shared" ref="T19" si="9">S19/R19</f>
-        <v>0.67304347826086963</v>
+        <f t="shared" ref="T19" si="8">S19/R19</f>
+        <v>1.0159305303929531</v>
       </c>
       <c r="U19" s="40">
         <f>S19/P19</f>
-        <v>1.7590909090909093</v>
+        <v>5.2458064516129035</v>
       </c>
       <c r="V19" s="43" t="e">
         <f>AVERAGE(V4:V18)</f>
@@ -2635,11 +2629,11 @@
         <v>17</v>
       </c>
       <c r="L20" s="9">
-        <f t="shared" ref="L20:L31" si="10">K20/J20</f>
+        <f t="shared" ref="L20:L31" si="9">K20/J20</f>
         <v>0.42499999999999999</v>
       </c>
       <c r="M20" s="7">
-        <f t="shared" ref="M20:M24" si="11">K20/H20</f>
+        <f t="shared" ref="M20:M24" si="10">K20/H20</f>
         <v>1.1333333333333333</v>
       </c>
       <c r="N20" s="10">
@@ -2652,7 +2646,7 @@
         <v>16</v>
       </c>
       <c r="Q20" s="9">
-        <f t="shared" ref="Q20:Q31" si="12">P20/O20</f>
+        <f t="shared" ref="Q20:Q31" si="11">P20/O20</f>
         <v>0.88888888888888884</v>
       </c>
       <c r="R20" s="7">
@@ -2662,11 +2656,11 @@
         <v>22</v>
       </c>
       <c r="T20" s="9">
-        <f t="shared" ref="T20:T31" si="13">S20/R20</f>
+        <f t="shared" ref="T20:T31" si="12">S20/R20</f>
         <v>0.88</v>
       </c>
       <c r="U20" s="7">
-        <f t="shared" ref="U20:U24" si="14">S20/P20</f>
+        <f t="shared" ref="U20:U24" si="13">S20/P20</f>
         <v>1.375</v>
       </c>
       <c r="V20" s="10">
@@ -2710,11 +2704,11 @@
         <v>13</v>
       </c>
       <c r="L21" s="13">
+        <f t="shared" si="9"/>
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="M21" s="11">
         <f t="shared" si="10"/>
-        <v>0.32500000000000001</v>
-      </c>
-      <c r="M21" s="11">
-        <f t="shared" si="11"/>
         <v>0.65</v>
       </c>
       <c r="N21" s="14">
@@ -2727,7 +2721,7 @@
         <v>14</v>
       </c>
       <c r="Q21" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0.93333333333333335</v>
       </c>
       <c r="R21" s="11">
@@ -2737,11 +2731,11 @@
         <v>19</v>
       </c>
       <c r="T21" s="13">
+        <f t="shared" si="12"/>
+        <v>0.95</v>
+      </c>
+      <c r="U21" s="11">
         <f t="shared" si="13"/>
-        <v>0.95</v>
-      </c>
-      <c r="U21" s="11">
-        <f t="shared" si="14"/>
         <v>1.3571428571428572</v>
       </c>
       <c r="V21" s="14">
@@ -2785,11 +2779,11 @@
         <v>20</v>
       </c>
       <c r="L22" s="13">
+        <f t="shared" si="9"/>
+        <v>0.5</v>
+      </c>
+      <c r="M22" s="11">
         <f t="shared" si="10"/>
-        <v>0.5</v>
-      </c>
-      <c r="M22" s="11">
-        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="N22" s="14">
@@ -2802,7 +2796,7 @@
         <v>15</v>
       </c>
       <c r="Q22" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0.88235294117647056</v>
       </c>
       <c r="R22" s="11">
@@ -2812,11 +2806,11 @@
         <v>20</v>
       </c>
       <c r="T22" s="13">
+        <f t="shared" si="12"/>
+        <v>0.86956521739130432</v>
+      </c>
+      <c r="U22" s="11">
         <f t="shared" si="13"/>
-        <v>0.86956521739130432</v>
-      </c>
-      <c r="U22" s="11">
-        <f t="shared" si="14"/>
         <v>1.3333333333333333</v>
       </c>
       <c r="V22" s="14">
@@ -2860,11 +2854,11 @@
         <v>60</v>
       </c>
       <c r="L23" s="13">
+        <f t="shared" si="9"/>
+        <v>1.5</v>
+      </c>
+      <c r="M23" s="11">
         <f t="shared" si="10"/>
-        <v>1.5</v>
-      </c>
-      <c r="M23" s="11">
-        <f t="shared" si="11"/>
         <v>2.6086956521739131</v>
       </c>
       <c r="N23" s="14">
@@ -2877,7 +2871,7 @@
         <v>15</v>
       </c>
       <c r="Q23" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0.88235294117647056</v>
       </c>
       <c r="R23" s="11">
@@ -2887,11 +2881,11 @@
         <v>19</v>
       </c>
       <c r="T23" s="13">
+        <f t="shared" si="12"/>
+        <v>0.90476190476190477</v>
+      </c>
+      <c r="U23" s="11">
         <f t="shared" si="13"/>
-        <v>0.90476190476190477</v>
-      </c>
-      <c r="U23" s="11">
-        <f t="shared" si="14"/>
         <v>1.2666666666666666</v>
       </c>
       <c r="V23" s="14">
@@ -2935,11 +2929,11 @@
         <v>13</v>
       </c>
       <c r="L24" s="38">
+        <f t="shared" si="9"/>
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="M24" s="36">
         <f t="shared" si="10"/>
-        <v>0.32500000000000001</v>
-      </c>
-      <c r="M24" s="36">
-        <f t="shared" si="11"/>
         <v>0.8666666666666667</v>
       </c>
       <c r="N24" s="39">
@@ -2952,7 +2946,7 @@
         <v>17</v>
       </c>
       <c r="Q24" s="38">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0.89473684210526316</v>
       </c>
       <c r="R24" s="36">
@@ -2962,11 +2956,11 @@
         <v>18</v>
       </c>
       <c r="T24" s="38">
+        <f t="shared" si="12"/>
+        <v>0.9</v>
+      </c>
+      <c r="U24" s="36">
         <f t="shared" si="13"/>
-        <v>0.9</v>
-      </c>
-      <c r="U24" s="36">
-        <f t="shared" si="14"/>
         <v>1.0588235294117647</v>
       </c>
       <c r="V24" s="39">
@@ -2994,7 +2988,7 @@
         <v>250</v>
       </c>
       <c r="H25" s="41">
-        <f t="shared" ref="H25" si="15">SUM(H20:H24)</f>
+        <f t="shared" ref="H25" si="14">SUM(H20:H24)</f>
         <v>93</v>
       </c>
       <c r="I25" s="42">
@@ -3006,11 +3000,11 @@
         <v>200</v>
       </c>
       <c r="K25" s="41">
-        <f t="shared" ref="K25" si="16">SUM(K20:K24)</f>
+        <f t="shared" ref="K25" si="15">SUM(K20:K24)</f>
         <v>123</v>
       </c>
       <c r="L25" s="42">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0.61499999999999999</v>
       </c>
       <c r="M25" s="40">
@@ -3026,11 +3020,11 @@
         <v>86</v>
       </c>
       <c r="P25" s="41">
-        <f t="shared" ref="P25" si="17">SUM(P20:P24)</f>
+        <f t="shared" ref="P25" si="16">SUM(P20:P24)</f>
         <v>77</v>
       </c>
       <c r="Q25" s="42">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0.89534883720930236</v>
       </c>
       <c r="R25" s="40">
@@ -3038,11 +3032,11 @@
         <v>109</v>
       </c>
       <c r="S25" s="41">
-        <f t="shared" ref="S25" si="18">SUM(S20:S24)</f>
+        <f t="shared" ref="S25" si="17">SUM(S20:S24)</f>
         <v>98</v>
       </c>
       <c r="T25" s="42">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0.8990825688073395</v>
       </c>
       <c r="U25" s="40">
@@ -3091,11 +3085,11 @@
         <v>15</v>
       </c>
       <c r="L26" s="9">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0.03</v>
       </c>
       <c r="M26" s="7">
-        <f t="shared" ref="M26:M29" si="19">K26/H26</f>
+        <f t="shared" ref="M26:M29" si="18">K26/H26</f>
         <v>1.6666666666666667</v>
       </c>
       <c r="N26" s="10">
@@ -3108,21 +3102,21 @@
         <v>0</v>
       </c>
       <c r="Q26" s="9">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="R26" s="7">
+        <v>47</v>
+      </c>
+      <c r="S26" s="8">
+        <v>0</v>
+      </c>
+      <c r="T26" s="9">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="R26" s="7">
-        <v>47</v>
-      </c>
-      <c r="S26" s="8">
-        <v>0</v>
-      </c>
-      <c r="T26" s="9">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
       <c r="U26" s="7" t="e">
-        <f t="shared" ref="U26:U29" si="20">S26/P26</f>
+        <f t="shared" ref="U26:U29" si="19">S26/P26</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V26" s="10">
@@ -3166,11 +3160,11 @@
         <v>8</v>
       </c>
       <c r="L27" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>1.6E-2</v>
       </c>
       <c r="M27" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="N27" s="14">
@@ -3183,7 +3177,7 @@
         <v>7</v>
       </c>
       <c r="Q27" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="R27" s="11">
@@ -3193,11 +3187,11 @@
         <v>7</v>
       </c>
       <c r="T27" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0.23333333333333334</v>
       </c>
       <c r="U27" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>1</v>
       </c>
       <c r="V27" s="14">
@@ -3241,11 +3235,11 @@
         <v>10</v>
       </c>
       <c r="L28" s="13">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0.02</v>
       </c>
       <c r="M28" s="11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>0.76923076923076927</v>
       </c>
       <c r="N28" s="14">
@@ -3258,7 +3252,7 @@
         <v>19</v>
       </c>
       <c r="Q28" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0.95</v>
       </c>
       <c r="R28" s="11">
@@ -3268,11 +3262,11 @@
         <v>13</v>
       </c>
       <c r="T28" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0.35135135135135137</v>
       </c>
       <c r="U28" s="11">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>0.68421052631578949</v>
       </c>
       <c r="V28" s="14">
@@ -3316,11 +3310,11 @@
         <v>11</v>
       </c>
       <c r="L29" s="38">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="M29" s="36">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>1</v>
       </c>
       <c r="N29" s="39">
@@ -3333,7 +3327,7 @@
         <v>10</v>
       </c>
       <c r="Q29" s="38">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>1.1111111111111112</v>
       </c>
       <c r="R29" s="36">
@@ -3343,11 +3337,11 @@
         <v>12</v>
       </c>
       <c r="T29" s="38">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0.75</v>
       </c>
       <c r="U29" s="36">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>1.2</v>
       </c>
       <c r="V29" s="39">
@@ -3375,7 +3369,7 @@
         <v>2400</v>
       </c>
       <c r="H30" s="41">
-        <f t="shared" ref="H30" si="21">SUM(H26:H29)</f>
+        <f t="shared" ref="H30" si="20">SUM(H26:H29)</f>
         <v>45</v>
       </c>
       <c r="I30" s="42">
@@ -3387,11 +3381,11 @@
         <v>2000</v>
       </c>
       <c r="K30" s="41">
-        <f t="shared" ref="K30" si="22">SUM(K26:K29)</f>
+        <f t="shared" ref="K30" si="21">SUM(K26:K29)</f>
         <v>44</v>
       </c>
       <c r="L30" s="42">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="M30" s="40">
@@ -3407,11 +3401,11 @@
         <v>63</v>
       </c>
       <c r="P30" s="41">
-        <f t="shared" ref="P30" si="23">SUM(P26:P29)</f>
+        <f t="shared" ref="P30" si="22">SUM(P26:P29)</f>
         <v>36</v>
       </c>
       <c r="Q30" s="42">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="R30" s="40">
@@ -3419,11 +3413,11 @@
         <v>130</v>
       </c>
       <c r="S30" s="41">
-        <f t="shared" ref="S30" si="24">SUM(S26:S29)</f>
+        <f t="shared" ref="S30" si="23">SUM(S26:S29)</f>
         <v>32</v>
       </c>
       <c r="T30" s="42">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0.24615384615384617</v>
       </c>
       <c r="U30" s="40">
@@ -3452,28 +3446,28 @@
         <v>3025</v>
       </c>
       <c r="H31" s="21">
-        <f t="shared" ref="H31" si="25">+H30+H25+H19</f>
-        <v>171</v>
+        <f t="shared" ref="H31" si="24">+H30+H25+H19</f>
+        <v>178</v>
       </c>
       <c r="I31" s="22">
         <f t="shared" si="0"/>
-        <v>5.6528925619834712E-2</v>
+        <v>5.8842975206611567E-2</v>
       </c>
       <c r="J31" s="20">
         <f>+J30+J25+J19</f>
         <v>2585</v>
       </c>
       <c r="K31" s="21">
-        <f t="shared" ref="K31" si="26">+K30+K25+K19</f>
-        <v>357.1</v>
+        <f t="shared" ref="K31" si="25">+K30+K25+K19</f>
+        <v>208.2</v>
       </c>
       <c r="L31" s="22">
-        <f t="shared" si="10"/>
-        <v>0.13814313346228241</v>
+        <f t="shared" si="9"/>
+        <v>8.0541586073500968E-2</v>
       </c>
       <c r="M31" s="20">
         <f>K31/H31</f>
-        <v>2.0883040935672517</v>
+        <v>1.1696629213483145</v>
       </c>
       <c r="N31" s="23" t="e">
         <f>AVERAGE(N30,N19,N25)</f>
@@ -3481,31 +3475,31 @@
       </c>
       <c r="O31" s="20">
         <f>+O30+O25+O19</f>
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="P31" s="21">
-        <f t="shared" ref="P31" si="27">+P30+P25+P19</f>
-        <v>157</v>
+        <f t="shared" ref="P31" si="26">+P30+P25+P19</f>
+        <v>144</v>
       </c>
       <c r="Q31" s="22">
-        <f t="shared" si="12"/>
-        <v>0.77339901477832518</v>
+        <f t="shared" si="11"/>
+        <v>0.79120879120879117</v>
       </c>
       <c r="R31" s="20">
         <f>+R30+R25+R19</f>
-        <v>354</v>
+        <v>399.07</v>
       </c>
       <c r="S31" s="21">
-        <f t="shared" ref="S31" si="28">+S30+S25+S19</f>
-        <v>207.4</v>
+        <f t="shared" ref="S31" si="27">+S30+S25+S19</f>
+        <v>292.62</v>
       </c>
       <c r="T31" s="22">
-        <f t="shared" si="13"/>
-        <v>0.58587570621468932</v>
+        <f t="shared" si="12"/>
+        <v>0.73325481745057264</v>
       </c>
       <c r="U31" s="20">
         <f>S31/P31</f>
-        <v>1.3210191082802547</v>
+        <v>2.0320833333333335</v>
       </c>
       <c r="V31" s="23" t="e">
         <f>AVERAGE(V30,V19,V25)</f>
@@ -3539,7 +3533,7 @@
     <col min="3" max="3" width="15.26953125" customWidth="1"/>
     <col min="4" max="4" width="18.26953125" customWidth="1"/>
     <col min="5" max="5" width="23.7265625" customWidth="1"/>
-    <col min="6" max="6" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.453125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.26953125" style="24" customWidth="1"/>
     <col min="8" max="8" width="10.54296875" customWidth="1"/>
     <col min="9" max="9" width="5.54296875" customWidth="1"/>
@@ -3570,18 +3564,18 @@
         <v>27</v>
       </c>
       <c r="B2" s="24">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.51851851851851849</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F2" s="94">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>40</v>
@@ -3687,23 +3681,23 @@
         <v>575</v>
       </c>
       <c r="K4" s="8">
-        <v>130.65</v>
+        <v>197.2</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.22721739130434784</v>
+        <v>0.34295652173913044</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>444.35</v>
+        <v>377.8</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>34.180769230769229</v>
+        <v>31.483333333333334</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.4357142857142857</v>
+        <v>2.1670329670329669</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3744,27 +3738,27 @@
         <v>550</v>
       </c>
       <c r="K5" s="12">
-        <v>81.52</v>
+        <v>96.27</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>0.1482181818181818</v>
+        <v>0.17503636363636363</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>468.48</v>
+        <v>453.73</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>36.036923076923081</v>
+        <v>37.810833333333335</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>1.1016216216216215</v>
+        <v>1.3009459459459458</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>1.2017690417690416</v>
+        <v>1.419213759213759</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3802,28 +3796,27 @@
         <v>550</v>
       </c>
       <c r="K6" s="12">
-        <f>11+0+3+15+5+12</f>
-        <v>46</v>
+        <v>46.32</v>
       </c>
       <c r="L6" s="71">
         <f t="shared" si="1"/>
-        <v>8.3636363636363634E-2</v>
+        <v>8.4218181818181817E-2</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="2"/>
-        <v>504</v>
+        <v>503.68</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>38.769230769230766</v>
+        <v>41.973333333333336</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
-        <v>1.6428571428571428</v>
+        <v>1.6542857142857144</v>
       </c>
       <c r="P6" s="14">
         <f t="shared" si="4"/>
-        <v>1.7922077922077921</v>
+        <v>1.8046753246753247</v>
       </c>
       <c r="Q6" s="34"/>
     </row>
@@ -3861,27 +3854,27 @@
         <v>550</v>
       </c>
       <c r="K7" s="12">
-        <v>35.799999999999997</v>
+        <v>46.77</v>
       </c>
       <c r="L7" s="71">
         <f t="shared" si="1"/>
-        <v>6.5090909090909088E-2</v>
+        <v>8.5036363636363646E-2</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" ref="M7:M31" si="5">J7-K7</f>
-        <v>514.20000000000005</v>
+        <v>503.23</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>39.553846153846159</v>
+        <v>41.935833333333335</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
-        <v>1.2344827586206895</v>
+        <v>1.6127586206896554</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="4"/>
-        <v>1.3467084639498432</v>
+        <v>1.7593730407523513</v>
       </c>
       <c r="Q7" s="34"/>
     </row>
@@ -3919,27 +3912,27 @@
         <v>575</v>
       </c>
       <c r="K8" s="12">
-        <v>215.6</v>
+        <v>220.95</v>
       </c>
       <c r="L8" s="71">
         <f t="shared" si="1"/>
-        <v>0.37495652173913041</v>
+        <v>0.38426086956521738</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>359.4</v>
+        <v>354.05</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>27.646153846153844</v>
+        <v>29.504166666666666</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
-        <v>2.2458333333333331</v>
+        <v>2.3015624999999997</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>2.3434782608695652</v>
+        <v>2.4016304347826085</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -3984,7 +3977,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>42.307692307692307</v>
+        <v>45.833333333333336</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4030,27 +4023,27 @@
         <v>4620</v>
       </c>
       <c r="K10" s="12">
-        <v>541.87</v>
+        <v>663.87</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>0.11728787878787879</v>
+        <v>0.14369480519480521</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>4078.13</v>
+        <v>3956.13</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>313.70230769230773</v>
+        <v>329.67750000000001</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>14.645135135135135</v>
+        <v>17.942432432432433</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>0.63398853398853405</v>
+        <v>0.77672867672867685</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4101,7 +4094,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>48.615384615384613</v>
+        <v>52.666666666666664</v>
       </c>
       <c r="O11" s="72">
         <f t="shared" si="4"/>
@@ -4158,7 +4151,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>40.846153846153847</v>
+        <v>44.25</v>
       </c>
       <c r="O12" s="72">
         <f t="shared" si="4"/>
@@ -4358,7 +4351,7 @@
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>92.307692307692307</v>
+        <v>100</v>
       </c>
       <c r="O16" s="72">
         <f t="shared" si="10"/>
@@ -4477,23 +4470,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>1388.44</v>
+        <v>1608.38</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>0.13012558575445174</v>
+        <v>0.15073851921274603</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>9281.56</v>
+        <v>9061.619999999999</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>713.96615384615382</v>
+        <v>755.13499999999988</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>3.5061616161616165</v>
+        <v>4.0615656565656568</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4546,7 +4539,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>35.769230769230766</v>
+        <v>38.75</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4602,7 +4595,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>35.92307692307692</v>
+        <v>38.916666666666664</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4658,7 +4651,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>35.692307692307693</v>
+        <v>38.666666666666664</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4714,7 +4707,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>36.384615384615387</v>
+        <v>39.416666666666664</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4770,7 +4763,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>37.230769230769234</v>
+        <v>40.333333333333336</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4826,7 +4819,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>181</v>
+        <v>196.08333333333334</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4883,7 +4876,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>47.384615384615387</v>
+        <v>51.333333333333336</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -4939,7 +4932,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>43.53846153846154</v>
+        <v>47.166666666666664</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -4995,7 +4988,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>44.153846153846153</v>
+        <v>47.833333333333336</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5051,7 +5044,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>47.07692307692308</v>
+        <v>51</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5107,7 +5100,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>182.15384615384616</v>
+        <v>197.33333333333334</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5148,23 +5141,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>1667.44</v>
+        <v>1887.38</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>0.10640970006381621</v>
+        <v>0.12044543714103383</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>14002.56</v>
+        <v>13782.619999999999</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>1077.1199999999999</v>
+        <v>1148.5516666666665</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>2.7930318257956448</v>
+        <v>3.1614405360134006</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>
